--- a/database/POs Pendentes.xlsx
+++ b/database/POs Pendentes.xlsx
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1299" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1300" uniqueCount="615">
   <si>
     <t>AA00002138134</t>
   </si>
@@ -1881,6 +1881,9 @@
   <si>
     <t>qntd_po</t>
   </si>
+  <si>
+    <t>company_id</t>
+  </si>
 </sst>
 </file>
 
@@ -2319,7 +2322,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:E8752"/>
+  <dimension ref="A1:F8752"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -2328,7 +2331,7 @@
     <col min="5" max="5" width="16.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15">
+    <row r="1" spans="1:6" ht="15">
       <c r="A1" s="1" t="s">
         <v>612</v>
       </c>
@@ -2344,8 +2347,11 @@
       <c r="E1" s="1" t="s">
         <v>609</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
@@ -2361,8 +2367,11 @@
       <c r="E2" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5">
+      <c r="F2" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
@@ -2378,8 +2387,11 @@
       <c r="E3" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:5">
+      <c r="F3" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="3" t="s">
         <v>3</v>
       </c>
@@ -2395,8 +2407,11 @@
       <c r="E4" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
+      <c r="F4" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
       <c r="A5" s="3" t="s">
         <v>4</v>
       </c>
@@ -2412,8 +2427,11 @@
       <c r="E5" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="3" t="s">
         <v>5</v>
       </c>
@@ -2429,8 +2447,11 @@
       <c r="E6" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
+      <c r="F6" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
         <v>6</v>
       </c>
@@ -2446,8 +2467,11 @@
       <c r="E7" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:5">
+      <c r="F7" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
         <v>7</v>
       </c>
@@ -2463,8 +2487,11 @@
       <c r="E8" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:5">
+      <c r="F8" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="3" t="s">
         <v>8</v>
       </c>
@@ -2480,8 +2507,11 @@
       <c r="E9" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="F9" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="3" t="s">
         <v>9</v>
       </c>
@@ -2497,8 +2527,11 @@
       <c r="E10" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="3" t="s">
         <v>10</v>
       </c>
@@ -2514,8 +2547,11 @@
       <c r="E11" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -2531,8 +2567,11 @@
       <c r="E12" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="F12" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="3" t="s">
         <v>12</v>
       </c>
@@ -2548,8 +2587,11 @@
       <c r="E13" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="F13" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="3" t="s">
         <v>13</v>
       </c>
@@ -2565,8 +2607,11 @@
       <c r="E14" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="F14" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" s="3" t="s">
         <v>14</v>
       </c>
@@ -2582,8 +2627,11 @@
       <c r="E15" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="F15" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
         <v>15</v>
       </c>
@@ -2599,8 +2647,11 @@
       <c r="E16" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="F16" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="3" t="s">
         <v>16</v>
       </c>
@@ -2616,8 +2667,11 @@
       <c r="E17" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="F17" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -2633,8 +2687,11 @@
       <c r="E18" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:5">
+      <c r="F18" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="3" t="s">
         <v>18</v>
       </c>
@@ -2650,8 +2707,11 @@
       <c r="E19" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:5">
+      <c r="F19" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
       <c r="A20" s="3" t="s">
         <v>19</v>
       </c>
@@ -2667,8 +2727,11 @@
       <c r="E20" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="21" spans="1:5">
+      <c r="F20" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
       <c r="A21" s="3" t="s">
         <v>20</v>
       </c>
@@ -2684,8 +2747,11 @@
       <c r="E21" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:5">
+      <c r="F21" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6">
       <c r="A22" s="3" t="s">
         <v>21</v>
       </c>
@@ -2701,8 +2767,11 @@
       <c r="E22" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:5">
+      <c r="F22" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
       <c r="A23" s="3" t="s">
         <v>22</v>
       </c>
@@ -2718,8 +2787,11 @@
       <c r="E23" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="3" t="s">
         <v>23</v>
       </c>
@@ -2735,8 +2807,11 @@
       <c r="E24" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="3" t="s">
         <v>24</v>
       </c>
@@ -2752,8 +2827,11 @@
       <c r="E25" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
+      <c r="F25" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
       <c r="A26" s="3" t="s">
         <v>25</v>
       </c>
@@ -2769,8 +2847,11 @@
       <c r="E26" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="3" t="s">
         <v>26</v>
       </c>
@@ -2786,8 +2867,11 @@
       <c r="E27" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="3" t="s">
         <v>27</v>
       </c>
@@ -2803,8 +2887,11 @@
       <c r="E28" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="3" t="s">
         <v>28</v>
       </c>
@@ -2820,8 +2907,11 @@
       <c r="E29" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="3" t="s">
         <v>29</v>
       </c>
@@ -2837,8 +2927,11 @@
       <c r="E30" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="1:5">
+      <c r="F30" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6">
       <c r="A31" s="3" t="s">
         <v>30</v>
       </c>
@@ -2854,8 +2947,11 @@
       <c r="E31" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="3" t="s">
         <v>31</v>
       </c>
@@ -2871,8 +2967,11 @@
       <c r="E32" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="33" spans="1:5">
+      <c r="F32" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="3" t="s">
         <v>32</v>
       </c>
@@ -2888,8 +2987,11 @@
       <c r="E33" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="3" t="s">
         <v>33</v>
       </c>
@@ -2905,8 +3007,11 @@
       <c r="E34" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="3" t="s">
         <v>33</v>
       </c>
@@ -2922,8 +3027,11 @@
       <c r="E35" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="36" spans="1:5">
+      <c r="F35" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="3" t="s">
         <v>33</v>
       </c>
@@ -2939,8 +3047,11 @@
       <c r="E36" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="1:5">
+      <c r="F36" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="3" t="s">
         <v>33</v>
       </c>
@@ -2956,8 +3067,11 @@
       <c r="E37" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="3" t="s">
         <v>33</v>
       </c>
@@ -2973,8 +3087,11 @@
       <c r="E38" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="39" spans="1:5">
+      <c r="F38" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6">
       <c r="A39" s="3" t="s">
         <v>33</v>
       </c>
@@ -2990,8 +3107,11 @@
       <c r="E39" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="40" spans="1:5">
+      <c r="F39" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6">
       <c r="A40" s="3" t="s">
         <v>34</v>
       </c>
@@ -3007,8 +3127,11 @@
       <c r="E40" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
+      <c r="F40" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6">
       <c r="A41" s="3" t="s">
         <v>35</v>
       </c>
@@ -3024,8 +3147,11 @@
       <c r="E41" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="42" spans="1:5">
+      <c r="F41" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6">
       <c r="A42" s="3" t="s">
         <v>38</v>
       </c>
@@ -3041,8 +3167,11 @@
       <c r="E42" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="43" spans="1:5">
+      <c r="F42" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6">
       <c r="A43" s="3" t="s">
         <v>39</v>
       </c>
@@ -3058,8 +3187,11 @@
       <c r="E43" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="44" spans="1:5">
+      <c r="F43" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6">
       <c r="A44" s="3" t="s">
         <v>40</v>
       </c>
@@ -3075,8 +3207,11 @@
       <c r="E44" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="45" spans="1:5">
+      <c r="F44" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
       <c r="A45" s="3" t="s">
         <v>42</v>
       </c>
@@ -3092,8 +3227,11 @@
       <c r="E45" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="F45" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
       <c r="A46" s="3" t="s">
         <v>43</v>
       </c>
@@ -3109,8 +3247,11 @@
       <c r="E46" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="47" spans="1:5">
+      <c r="F46" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
       <c r="A47" s="3" t="s">
         <v>44</v>
       </c>
@@ -3126,8 +3267,11 @@
       <c r="E47" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="48" spans="1:5">
+      <c r="F47" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6">
       <c r="A48" s="3" t="s">
         <v>45</v>
       </c>
@@ -3143,8 +3287,11 @@
       <c r="E48" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="49" spans="1:5">
+      <c r="F48" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6">
       <c r="A49" s="3" t="s">
         <v>46</v>
       </c>
@@ -3160,8 +3307,11 @@
       <c r="E49" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="50" spans="1:5">
+      <c r="F49" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6">
       <c r="A50" s="3" t="s">
         <v>47</v>
       </c>
@@ -3177,8 +3327,11 @@
       <c r="E50" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="51" spans="1:5">
+      <c r="F50" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6">
       <c r="A51" s="3" t="s">
         <v>49</v>
       </c>
@@ -3194,8 +3347,11 @@
       <c r="E51" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="52" spans="1:5">
+      <c r="F51" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6">
       <c r="A52" s="3" t="s">
         <v>52</v>
       </c>
@@ -3211,8 +3367,11 @@
       <c r="E52" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="53" spans="1:5">
+      <c r="F52" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6">
       <c r="A53" s="3" t="s">
         <v>54</v>
       </c>
@@ -3228,8 +3387,11 @@
       <c r="E53" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="1:5">
+      <c r="F53" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6">
       <c r="A54" s="3" t="s">
         <v>53</v>
       </c>
@@ -3245,8 +3407,11 @@
       <c r="E54" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="55" spans="1:5">
+      <c r="F54" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6">
       <c r="A55" s="3" t="s">
         <v>55</v>
       </c>
@@ -3262,8 +3427,11 @@
       <c r="E55" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="56" spans="1:5">
+      <c r="F55" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6">
       <c r="A56" s="3" t="s">
         <v>57</v>
       </c>
@@ -3279,8 +3447,11 @@
       <c r="E56" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="57" spans="1:5">
+      <c r="F56" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6">
       <c r="A57" s="3" t="s">
         <v>58</v>
       </c>
@@ -3296,8 +3467,11 @@
       <c r="E57" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="58" spans="1:5">
+      <c r="F57" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6">
       <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
@@ -3313,8 +3487,11 @@
       <c r="E58" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="59" spans="1:5">
+      <c r="F58" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6">
       <c r="A59" s="3" t="s">
         <v>61</v>
       </c>
@@ -3330,8 +3507,11 @@
       <c r="E59" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="60" spans="1:5">
+      <c r="F59" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6">
       <c r="A60" s="3" t="s">
         <v>62</v>
       </c>
@@ -3347,8 +3527,11 @@
       <c r="E60" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="61" spans="1:5">
+      <c r="F60" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6">
       <c r="A61" s="3" t="s">
         <v>63</v>
       </c>
@@ -3364,8 +3547,11 @@
       <c r="E61" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="62" spans="1:5">
+      <c r="F61" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6">
       <c r="A62" s="3" t="s">
         <v>64</v>
       </c>
@@ -3381,8 +3567,11 @@
       <c r="E62" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="63" spans="1:5">
+      <c r="F62" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6">
       <c r="A63" s="3" t="s">
         <v>65</v>
       </c>
@@ -3398,8 +3587,11 @@
       <c r="E63" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="64" spans="1:5">
+      <c r="F63" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6">
       <c r="A64" s="3" t="s">
         <v>66</v>
       </c>
@@ -3415,8 +3607,11 @@
       <c r="E64" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="65" spans="1:5">
+      <c r="F64" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6">
       <c r="A65" s="3" t="s">
         <v>67</v>
       </c>
@@ -3432,8 +3627,11 @@
       <c r="E65" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="66" spans="1:5">
+      <c r="F65" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6">
       <c r="A66" s="3" t="s">
         <v>59</v>
       </c>
@@ -3449,8 +3647,11 @@
       <c r="E66" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="67" spans="1:5">
+      <c r="F66" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6">
       <c r="A67" s="3" t="s">
         <v>68</v>
       </c>
@@ -3466,8 +3667,11 @@
       <c r="E67" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="68" spans="1:5">
+      <c r="F67" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6">
       <c r="A68" s="3" t="s">
         <v>70</v>
       </c>
@@ -3483,8 +3687,11 @@
       <c r="E68" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="69" spans="1:5">
+      <c r="F68" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6">
       <c r="A69" s="3" t="s">
         <v>71</v>
       </c>
@@ -3500,8 +3707,11 @@
       <c r="E69" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="70" spans="1:5">
+      <c r="F69" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6">
       <c r="A70" s="3" t="s">
         <v>72</v>
       </c>
@@ -3517,8 +3727,11 @@
       <c r="E70" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="71" spans="1:5">
+      <c r="F70" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6">
       <c r="A71" s="3" t="s">
         <v>73</v>
       </c>
@@ -3534,8 +3747,11 @@
       <c r="E71" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="72" spans="1:5">
+      <c r="F71" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6">
       <c r="A72" s="3" t="s">
         <v>74</v>
       </c>
@@ -3551,8 +3767,11 @@
       <c r="E72" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="73" spans="1:5">
+      <c r="F72" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6">
       <c r="A73" s="3" t="s">
         <v>75</v>
       </c>
@@ -3568,8 +3787,11 @@
       <c r="E73" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="74" spans="1:5">
+      <c r="F73" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6">
       <c r="A74" s="3" t="s">
         <v>76</v>
       </c>
@@ -3585,8 +3807,11 @@
       <c r="E74" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="75" spans="1:5">
+      <c r="F74" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6">
       <c r="A75" s="3" t="s">
         <v>77</v>
       </c>
@@ -3602,8 +3827,11 @@
       <c r="E75" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="76" spans="1:5">
+      <c r="F75" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6">
       <c r="A76" s="3" t="s">
         <v>78</v>
       </c>
@@ -3619,8 +3847,11 @@
       <c r="E76" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="77" spans="1:5">
+      <c r="F76" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6">
       <c r="A77" s="3" t="s">
         <v>79</v>
       </c>
@@ -3636,8 +3867,11 @@
       <c r="E77" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="78" spans="1:5">
+      <c r="F77" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6">
       <c r="A78" s="3" t="s">
         <v>80</v>
       </c>
@@ -3653,8 +3887,11 @@
       <c r="E78" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="79" spans="1:5">
+      <c r="F78" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6">
       <c r="A79" s="3" t="s">
         <v>81</v>
       </c>
@@ -3670,8 +3907,11 @@
       <c r="E79" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="80" spans="1:5">
+      <c r="F79" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6">
       <c r="A80" s="3" t="s">
         <v>82</v>
       </c>
@@ -3687,8 +3927,11 @@
       <c r="E80" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="81" spans="1:5">
+      <c r="F80" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6">
       <c r="A81" s="3" t="s">
         <v>83</v>
       </c>
@@ -3704,8 +3947,11 @@
       <c r="E81" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="82" spans="1:5">
+      <c r="F81" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6">
       <c r="A82" s="3" t="s">
         <v>84</v>
       </c>
@@ -3721,8 +3967,11 @@
       <c r="E82" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="83" spans="1:5">
+      <c r="F82" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6">
       <c r="A83" s="3" t="s">
         <v>85</v>
       </c>
@@ -3738,8 +3987,11 @@
       <c r="E83" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="84" spans="1:5">
+      <c r="F83" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6">
       <c r="A84" s="3" t="s">
         <v>86</v>
       </c>
@@ -3755,8 +4007,11 @@
       <c r="E84" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="85" spans="1:5">
+      <c r="F84" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6">
       <c r="A85" s="3" t="s">
         <v>87</v>
       </c>
@@ -3772,8 +4027,11 @@
       <c r="E85" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="86" spans="1:5">
+      <c r="F85" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6">
       <c r="A86" s="3" t="s">
         <v>88</v>
       </c>
@@ -3789,8 +4047,11 @@
       <c r="E86" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="87" spans="1:5">
+      <c r="F86" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6">
       <c r="A87" s="3" t="s">
         <v>89</v>
       </c>
@@ -3806,8 +4067,11 @@
       <c r="E87" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="88" spans="1:5">
+      <c r="F87" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6">
       <c r="A88" s="3" t="s">
         <v>90</v>
       </c>
@@ -3823,8 +4087,11 @@
       <c r="E88" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="89" spans="1:5">
+      <c r="F88" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6">
       <c r="A89" s="3" t="s">
         <v>91</v>
       </c>
@@ -3840,8 +4107,11 @@
       <c r="E89" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="90" spans="1:5">
+      <c r="F89" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6">
       <c r="A90" s="3" t="s">
         <v>92</v>
       </c>
@@ -3857,8 +4127,11 @@
       <c r="E90" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="91" spans="1:5">
+      <c r="F90" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6">
       <c r="A91" s="3" t="s">
         <v>93</v>
       </c>
@@ -3874,8 +4147,11 @@
       <c r="E91" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="92" spans="1:5">
+      <c r="F91" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6">
       <c r="A92" s="3" t="s">
         <v>94</v>
       </c>
@@ -3891,8 +4167,11 @@
       <c r="E92" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="93" spans="1:5">
+      <c r="F92" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6">
       <c r="A93" s="3" t="s">
         <v>98</v>
       </c>
@@ -3908,8 +4187,11 @@
       <c r="E93" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="94" spans="1:5">
+      <c r="F93" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6">
       <c r="A94" s="3" t="s">
         <v>99</v>
       </c>
@@ -3925,8 +4207,11 @@
       <c r="E94" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="95" spans="1:5">
+      <c r="F94" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6">
       <c r="A95" s="3" t="s">
         <v>100</v>
       </c>
@@ -3942,8 +4227,11 @@
       <c r="E95" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="96" spans="1:5">
+      <c r="F95" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6">
       <c r="A96" s="3" t="s">
         <v>101</v>
       </c>
@@ -3959,8 +4247,11 @@
       <c r="E96" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="97" spans="1:5">
+      <c r="F96" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6">
       <c r="A97" s="3" t="s">
         <v>102</v>
       </c>
@@ -3976,8 +4267,11 @@
       <c r="E97" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="98" spans="1:5">
+      <c r="F97" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6">
       <c r="A98" s="3" t="s">
         <v>103</v>
       </c>
@@ -3993,8 +4287,11 @@
       <c r="E98" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="99" spans="1:5">
+      <c r="F98" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6">
       <c r="A99" s="3" t="s">
         <v>104</v>
       </c>
@@ -4010,8 +4307,11 @@
       <c r="E99" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="100" spans="1:5">
+      <c r="F99" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6">
       <c r="A100" s="3" t="s">
         <v>126</v>
       </c>
@@ -4027,8 +4327,11 @@
       <c r="E100" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="101" spans="1:5">
+      <c r="F100" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6">
       <c r="A101" s="3" t="s">
         <v>130</v>
       </c>
@@ -4044,8 +4347,11 @@
       <c r="E101" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="102" spans="1:5">
+      <c r="F101" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6">
       <c r="A102" s="3" t="s">
         <v>138</v>
       </c>
@@ -4061,8 +4367,11 @@
       <c r="E102" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="103" spans="1:5">
+      <c r="F102" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6">
       <c r="A103" s="3" t="s">
         <v>107</v>
       </c>
@@ -4078,8 +4387,11 @@
       <c r="E103" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="104" spans="1:5">
+      <c r="F103" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6">
       <c r="A104" s="3" t="s">
         <v>108</v>
       </c>
@@ -4095,8 +4407,11 @@
       <c r="E104" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="105" spans="1:5">
+      <c r="F104" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6">
       <c r="A105" s="3" t="s">
         <v>109</v>
       </c>
@@ -4112,8 +4427,11 @@
       <c r="E105" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="106" spans="1:5">
+      <c r="F105" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6">
       <c r="A106" s="3" t="s">
         <v>111</v>
       </c>
@@ -4129,8 +4447,11 @@
       <c r="E106" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="107" spans="1:5">
+      <c r="F106" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6">
       <c r="A107" s="3" t="s">
         <v>112</v>
       </c>
@@ -4146,8 +4467,11 @@
       <c r="E107" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="108" spans="1:5">
+      <c r="F107" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6">
       <c r="A108" s="3" t="s">
         <v>113</v>
       </c>
@@ -4163,8 +4487,11 @@
       <c r="E108" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="109" spans="1:5">
+      <c r="F108" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6">
       <c r="A109" s="3" t="s">
         <v>114</v>
       </c>
@@ -4180,8 +4507,11 @@
       <c r="E109" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="110" spans="1:5">
+      <c r="F109" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6">
       <c r="A110" s="3" t="s">
         <v>115</v>
       </c>
@@ -4197,8 +4527,11 @@
       <c r="E110" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="111" spans="1:5">
+      <c r="F110" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6">
       <c r="A111" s="3" t="s">
         <v>116</v>
       </c>
@@ -4214,8 +4547,11 @@
       <c r="E111" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="112" spans="1:5">
+      <c r="F111" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6">
       <c r="A112" s="3" t="s">
         <v>117</v>
       </c>
@@ -4231,8 +4567,11 @@
       <c r="E112" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="113" spans="1:5">
+      <c r="F112" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" s="3" t="s">
         <v>118</v>
       </c>
@@ -4248,8 +4587,11 @@
       <c r="E113" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="114" spans="1:5">
+      <c r="F113" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" s="3" t="s">
         <v>119</v>
       </c>
@@ -4265,8 +4607,11 @@
       <c r="E114" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="115" spans="1:5">
+      <c r="F114" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" s="3" t="s">
         <v>120</v>
       </c>
@@ -4282,8 +4627,11 @@
       <c r="E115" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="116" spans="1:5">
+      <c r="F115" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" s="3" t="s">
         <v>121</v>
       </c>
@@ -4299,8 +4647,11 @@
       <c r="E116" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="117" spans="1:5">
+      <c r="F116" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" s="3" t="s">
         <v>122</v>
       </c>
@@ -4316,8 +4667,11 @@
       <c r="E117" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="118" spans="1:5">
+      <c r="F117" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" s="3" t="s">
         <v>123</v>
       </c>
@@ -4333,8 +4687,11 @@
       <c r="E118" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="119" spans="1:5">
+      <c r="F118" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" s="3" t="s">
         <v>124</v>
       </c>
@@ -4350,8 +4707,11 @@
       <c r="E119" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="120" spans="1:5">
+      <c r="F119" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" s="3" t="s">
         <v>125</v>
       </c>
@@ -4367,8 +4727,11 @@
       <c r="E120" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="121" spans="1:5">
+      <c r="F120" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" s="3" t="s">
         <v>126</v>
       </c>
@@ -4384,8 +4747,11 @@
       <c r="E121" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="122" spans="1:5">
+      <c r="F121" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" s="3" t="s">
         <v>127</v>
       </c>
@@ -4401,8 +4767,11 @@
       <c r="E122" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="123" spans="1:5">
+      <c r="F122" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" s="3" t="s">
         <v>128</v>
       </c>
@@ -4418,8 +4787,11 @@
       <c r="E123" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="124" spans="1:5">
+      <c r="F123" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" s="3" t="s">
         <v>130</v>
       </c>
@@ -4435,8 +4807,11 @@
       <c r="E124" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="125" spans="1:5">
+      <c r="F124" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" s="3" t="s">
         <v>131</v>
       </c>
@@ -4452,8 +4827,11 @@
       <c r="E125" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="126" spans="1:5">
+      <c r="F125" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" s="3" t="s">
         <v>132</v>
       </c>
@@ -4469,8 +4847,11 @@
       <c r="E126" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="127" spans="1:5">
+      <c r="F126" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" s="3" t="s">
         <v>133</v>
       </c>
@@ -4486,8 +4867,11 @@
       <c r="E127" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="128" spans="1:5">
+      <c r="F127" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" s="3" t="s">
         <v>134</v>
       </c>
@@ -4503,8 +4887,11 @@
       <c r="E128" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="129" spans="1:5">
+      <c r="F128" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6">
       <c r="A129" s="3" t="s">
         <v>135</v>
       </c>
@@ -4520,8 +4907,11 @@
       <c r="E129" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="130" spans="1:5">
+      <c r="F129" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6">
       <c r="A130" s="3" t="s">
         <v>136</v>
       </c>
@@ -4537,8 +4927,11 @@
       <c r="E130" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="131" spans="1:5">
+      <c r="F130" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6">
       <c r="A131" s="3" t="s">
         <v>137</v>
       </c>
@@ -4554,8 +4947,11 @@
       <c r="E131" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="132" spans="1:5">
+      <c r="F131" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6">
       <c r="A132" s="3" t="s">
         <v>138</v>
       </c>
@@ -4571,8 +4967,11 @@
       <c r="E132" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="133" spans="1:5">
+      <c r="F132" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6">
       <c r="A133" s="3" t="s">
         <v>139</v>
       </c>
@@ -4588,8 +4987,11 @@
       <c r="E133" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="134" spans="1:5">
+      <c r="F133" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6">
       <c r="A134" s="3" t="s">
         <v>110</v>
       </c>
@@ -4605,8 +5007,11 @@
       <c r="E134" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="135" spans="1:5">
+      <c r="F134" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6">
       <c r="A135" s="3" t="s">
         <v>129</v>
       </c>
@@ -4622,8 +5027,11 @@
       <c r="E135" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="136" spans="1:5">
+      <c r="F135" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6">
       <c r="A136" s="3" t="s">
         <v>51</v>
       </c>
@@ -4639,8 +5047,11 @@
       <c r="E136" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="137" spans="1:5">
+      <c r="F136" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6">
       <c r="A137" s="3" t="s">
         <v>142</v>
       </c>
@@ -4656,8 +5067,11 @@
       <c r="E137" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="138" spans="1:5">
+      <c r="F137" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6">
       <c r="A138" s="3" t="s">
         <v>48</v>
       </c>
@@ -4673,8 +5087,11 @@
       <c r="E138" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="139" spans="1:5">
+      <c r="F138" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6">
       <c r="A139" s="3" t="s">
         <v>143</v>
       </c>
@@ -4690,8 +5107,11 @@
       <c r="E139" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="140" spans="1:5">
+      <c r="F139" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6">
       <c r="A140" s="3" t="s">
         <v>144</v>
       </c>
@@ -4707,8 +5127,11 @@
       <c r="E140" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="141" spans="1:5">
+      <c r="F140" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6">
       <c r="A141" s="3" t="s">
         <v>145</v>
       </c>
@@ -4724,8 +5147,11 @@
       <c r="E141" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="142" spans="1:5">
+      <c r="F141" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6">
       <c r="A142" s="3" t="s">
         <v>146</v>
       </c>
@@ -4741,8 +5167,11 @@
       <c r="E142" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="143" spans="1:5">
+      <c r="F142" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6">
       <c r="A143" s="3" t="s">
         <v>167</v>
       </c>
@@ -4758,8 +5187,11 @@
       <c r="E143" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="144" spans="1:5">
+      <c r="F143" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6">
       <c r="A144" s="3" t="s">
         <v>168</v>
       </c>
@@ -4775,8 +5207,11 @@
       <c r="E144" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="145" spans="1:5">
+      <c r="F144" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6">
       <c r="A145" s="3" t="s">
         <v>166</v>
       </c>
@@ -4792,8 +5227,11 @@
       <c r="E145" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="146" spans="1:5">
+      <c r="F145" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6">
       <c r="A146" s="3" t="s">
         <v>167</v>
       </c>
@@ -4809,8 +5247,11 @@
       <c r="E146" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="147" spans="1:5">
+      <c r="F146" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6">
       <c r="A147" s="3" t="s">
         <v>168</v>
       </c>
@@ -4826,8 +5267,11 @@
       <c r="E147" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="148" spans="1:5">
+      <c r="F147" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6">
       <c r="A148" s="3" t="s">
         <v>170</v>
       </c>
@@ -4843,8 +5287,11 @@
       <c r="E148" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="149" spans="1:5">
+      <c r="F148" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6">
       <c r="A149" s="3" t="s">
         <v>171</v>
       </c>
@@ -4860,8 +5307,11 @@
       <c r="E149" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="150" spans="1:5">
+      <c r="F149" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6">
       <c r="A150" s="3" t="s">
         <v>169</v>
       </c>
@@ -4877,8 +5327,11 @@
       <c r="E150" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="151" spans="1:5">
+      <c r="F150" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6">
       <c r="A151" s="3" t="s">
         <v>172</v>
       </c>
@@ -4894,8 +5347,11 @@
       <c r="E151" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="152" spans="1:5">
+      <c r="F151" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6">
       <c r="A152" s="3" t="s">
         <v>173</v>
       </c>
@@ -4911,8 +5367,11 @@
       <c r="E152" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="153" spans="1:5">
+      <c r="F152" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6">
       <c r="A153" s="3" t="s">
         <v>174</v>
       </c>
@@ -4928,8 +5387,11 @@
       <c r="E153" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="154" spans="1:5">
+      <c r="F153" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6">
       <c r="A154" s="3" t="s">
         <v>175</v>
       </c>
@@ -4945,8 +5407,11 @@
       <c r="E154" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="155" spans="1:5">
+      <c r="F154" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6">
       <c r="A155" s="3" t="s">
         <v>176</v>
       </c>
@@ -4962,8 +5427,11 @@
       <c r="E155" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="156" spans="1:5">
+      <c r="F155" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6">
       <c r="A156" s="3" t="s">
         <v>177</v>
       </c>
@@ -4979,8 +5447,11 @@
       <c r="E156" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="157" spans="1:5">
+      <c r="F156" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6">
       <c r="A157" s="3" t="s">
         <v>178</v>
       </c>
@@ -4996,8 +5467,11 @@
       <c r="E157" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="158" spans="1:5">
+      <c r="F157" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6">
       <c r="A158" s="3" t="s">
         <v>179</v>
       </c>
@@ -5013,8 +5487,11 @@
       <c r="E158" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="159" spans="1:5">
+      <c r="F158" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6">
       <c r="A159" s="3" t="s">
         <v>180</v>
       </c>
@@ -5030,8 +5507,11 @@
       <c r="E159" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="160" spans="1:5">
+      <c r="F159" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6">
       <c r="A160" s="3" t="s">
         <v>181</v>
       </c>
@@ -5047,8 +5527,11 @@
       <c r="E160" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="161" spans="1:5">
+      <c r="F160" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6">
       <c r="A161" s="3" t="s">
         <v>182</v>
       </c>
@@ -5064,8 +5547,11 @@
       <c r="E161" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="162" spans="1:5">
+      <c r="F161" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6">
       <c r="A162" s="3" t="s">
         <v>183</v>
       </c>
@@ -5081,8 +5567,11 @@
       <c r="E162" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="163" spans="1:5">
+      <c r="F162" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6">
       <c r="A163" s="3" t="s">
         <v>184</v>
       </c>
@@ -5098,8 +5587,11 @@
       <c r="E163" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="164" spans="1:5">
+      <c r="F163" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6">
       <c r="A164" s="3" t="s">
         <v>185</v>
       </c>
@@ -5115,8 +5607,11 @@
       <c r="E164" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="165" spans="1:5">
+      <c r="F164" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6">
       <c r="A165" s="3" t="s">
         <v>186</v>
       </c>
@@ -5132,8 +5627,11 @@
       <c r="E165" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="166" spans="1:5">
+      <c r="F165" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6">
       <c r="A166" s="3" t="s">
         <v>187</v>
       </c>
@@ -5149,8 +5647,11 @@
       <c r="E166" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="167" spans="1:5">
+      <c r="F166" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6">
       <c r="A167" s="3" t="s">
         <v>188</v>
       </c>
@@ -5166,8 +5667,11 @@
       <c r="E167" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="168" spans="1:5">
+      <c r="F167" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6">
       <c r="A168" s="3" t="s">
         <v>189</v>
       </c>
@@ -5183,8 +5687,11 @@
       <c r="E168" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="169" spans="1:5">
+      <c r="F168" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6">
       <c r="A169" s="3" t="s">
         <v>190</v>
       </c>
@@ -5200,8 +5707,11 @@
       <c r="E169" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="170" spans="1:5">
+      <c r="F169" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6">
       <c r="A170" s="3" t="s">
         <v>192</v>
       </c>
@@ -5217,8 +5727,11 @@
       <c r="E170" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="171" spans="1:5">
+      <c r="F170" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6">
       <c r="A171" s="3" t="s">
         <v>193</v>
       </c>
@@ -5234,8 +5747,11 @@
       <c r="E171" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="172" spans="1:5">
+      <c r="F171" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6">
       <c r="A172" s="3" t="s">
         <v>194</v>
       </c>
@@ -5251,8 +5767,11 @@
       <c r="E172" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="173" spans="1:5">
+      <c r="F172" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6">
       <c r="A173" s="3" t="s">
         <v>195</v>
       </c>
@@ -5268,8 +5787,11 @@
       <c r="E173" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="174" spans="1:5">
+      <c r="F173" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6">
       <c r="A174" s="3" t="s">
         <v>196</v>
       </c>
@@ -5285,8 +5807,11 @@
       <c r="E174" s="4" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="175" spans="1:5">
+      <c r="F174" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6">
       <c r="A175" s="3" t="s">
         <v>198</v>
       </c>
@@ -5302,8 +5827,11 @@
       <c r="E175" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="176" spans="1:5">
+      <c r="F175" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6">
       <c r="A176" s="3" t="s">
         <v>199</v>
       </c>
@@ -5319,8 +5847,11 @@
       <c r="E176" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="177" spans="1:5">
+      <c r="F176" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6">
       <c r="A177" s="3" t="s">
         <v>200</v>
       </c>
@@ -5336,8 +5867,11 @@
       <c r="E177" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="178" spans="1:5">
+      <c r="F177" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6">
       <c r="A178" s="3" t="s">
         <v>201</v>
       </c>
@@ -5353,8 +5887,11 @@
       <c r="E178" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="179" spans="1:5">
+      <c r="F178" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6">
       <c r="A179" s="3" t="s">
         <v>202</v>
       </c>
@@ -5370,8 +5907,11 @@
       <c r="E179" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="180" spans="1:5">
+      <c r="F179" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6">
       <c r="A180" s="3" t="s">
         <v>203</v>
       </c>
@@ -5387,8 +5927,11 @@
       <c r="E180" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="181" spans="1:5">
+      <c r="F180" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6">
       <c r="A181" s="3" t="s">
         <v>204</v>
       </c>
@@ -5404,8 +5947,11 @@
       <c r="E181" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="182" spans="1:5">
+      <c r="F181" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6">
       <c r="A182" s="3" t="s">
         <v>205</v>
       </c>
@@ -5421,8 +5967,11 @@
       <c r="E182" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="183" spans="1:5">
+      <c r="F182" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6">
       <c r="A183" s="3" t="s">
         <v>206</v>
       </c>
@@ -5438,8 +5987,11 @@
       <c r="E183" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="184" spans="1:5">
+      <c r="F183" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6">
       <c r="A184" s="3" t="s">
         <v>207</v>
       </c>
@@ -5455,8 +6007,11 @@
       <c r="E184" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="185" spans="1:5">
+      <c r="F184" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6">
       <c r="A185" s="3" t="s">
         <v>208</v>
       </c>
@@ -5472,8 +6027,11 @@
       <c r="E185" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="186" spans="1:5">
+      <c r="F185" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6">
       <c r="A186" s="3" t="s">
         <v>209</v>
       </c>
@@ -5489,8 +6047,11 @@
       <c r="E186" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="187" spans="1:5">
+      <c r="F186" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6">
       <c r="A187" s="3" t="s">
         <v>210</v>
       </c>
@@ -5506,8 +6067,11 @@
       <c r="E187" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="188" spans="1:5">
+      <c r="F187" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6">
       <c r="A188" s="3" t="s">
         <v>211</v>
       </c>
@@ -5523,8 +6087,11 @@
       <c r="E188" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="189" spans="1:5">
+      <c r="F188" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6">
       <c r="A189" s="3" t="s">
         <v>212</v>
       </c>
@@ -5540,8 +6107,11 @@
       <c r="E189" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="190" spans="1:5">
+      <c r="F189" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6">
       <c r="A190" s="3" t="s">
         <v>213</v>
       </c>
@@ -5557,8 +6127,11 @@
       <c r="E190" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="191" spans="1:5">
+      <c r="F190" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6">
       <c r="A191" s="3" t="s">
         <v>214</v>
       </c>
@@ -5574,8 +6147,11 @@
       <c r="E191" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="192" spans="1:5">
+      <c r="F191" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6">
       <c r="A192" s="3" t="s">
         <v>215</v>
       </c>
@@ -5591,8 +6167,11 @@
       <c r="E192" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="193" spans="1:5">
+      <c r="F192" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6">
       <c r="A193" s="3" t="s">
         <v>216</v>
       </c>
@@ -5608,8 +6187,11 @@
       <c r="E193" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="194" spans="1:5">
+      <c r="F193" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6">
       <c r="A194" s="3" t="s">
         <v>217</v>
       </c>
@@ -5625,8 +6207,11 @@
       <c r="E194" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="195" spans="1:5">
+      <c r="F194" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6">
       <c r="A195" s="3" t="s">
         <v>218</v>
       </c>
@@ -5642,8 +6227,11 @@
       <c r="E195" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="196" spans="1:5">
+      <c r="F195" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6">
       <c r="A196" s="3" t="s">
         <v>219</v>
       </c>
@@ -5659,8 +6247,11 @@
       <c r="E196" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="197" spans="1:5">
+      <c r="F196" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6">
       <c r="A197" s="3" t="s">
         <v>220</v>
       </c>
@@ -5676,8 +6267,11 @@
       <c r="E197" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="198" spans="1:5">
+      <c r="F197" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6">
       <c r="A198" s="3" t="s">
         <v>241</v>
       </c>
@@ -5693,8 +6287,11 @@
       <c r="E198" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="199" spans="1:5">
+      <c r="F198" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6">
       <c r="A199" s="3" t="s">
         <v>243</v>
       </c>
@@ -5710,8 +6307,11 @@
       <c r="E199" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="200" spans="1:5">
+      <c r="F199" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6">
       <c r="A200" s="3" t="s">
         <v>244</v>
       </c>
@@ -5727,8 +6327,11 @@
       <c r="E200" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="201" spans="1:5">
+      <c r="F200" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6">
       <c r="A201" s="3" t="s">
         <v>245</v>
       </c>
@@ -5744,8 +6347,11 @@
       <c r="E201" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="202" spans="1:5">
+      <c r="F201" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6">
       <c r="A202" s="3" t="s">
         <v>246</v>
       </c>
@@ -5761,8 +6367,11 @@
       <c r="E202" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="203" spans="1:5">
+      <c r="F202" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6">
       <c r="A203" s="3" t="s">
         <v>249</v>
       </c>
@@ -5778,8 +6387,11 @@
       <c r="E203" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="204" spans="1:5">
+      <c r="F203" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6">
       <c r="A204" s="3" t="s">
         <v>251</v>
       </c>
@@ -5795,8 +6407,11 @@
       <c r="E204" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="205" spans="1:5">
+      <c r="F204" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6">
       <c r="A205" s="3" t="s">
         <v>253</v>
       </c>
@@ -5812,8 +6427,11 @@
       <c r="E205" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="206" spans="1:5">
+      <c r="F205" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6">
       <c r="A206" s="3" t="s">
         <v>254</v>
       </c>
@@ -5829,8 +6447,11 @@
       <c r="E206" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="207" spans="1:5">
+      <c r="F206" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6">
       <c r="A207" s="3" t="s">
         <v>256</v>
       </c>
@@ -5846,8 +6467,11 @@
       <c r="E207" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="208" spans="1:5">
+      <c r="F207" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6">
       <c r="A208" s="3" t="s">
         <v>257</v>
       </c>
@@ -5863,8 +6487,11 @@
       <c r="E208" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="209" spans="1:5">
+      <c r="F208" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6">
       <c r="A209" s="3" t="s">
         <v>262</v>
       </c>
@@ -5880,8 +6507,11 @@
       <c r="E209" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="210" spans="1:5">
+      <c r="F209" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6">
       <c r="A210" s="3" t="s">
         <v>264</v>
       </c>
@@ -5897,8 +6527,11 @@
       <c r="E210" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="211" spans="1:5">
+      <c r="F210" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6">
       <c r="A211" s="3" t="s">
         <v>265</v>
       </c>
@@ -5914,8 +6547,11 @@
       <c r="E211" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="212" spans="1:5">
+      <c r="F211" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6">
       <c r="A212" s="3" t="s">
         <v>267</v>
       </c>
@@ -5931,8 +6567,11 @@
       <c r="E212" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="213" spans="1:5">
+      <c r="F212" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6">
       <c r="A213" s="3" t="s">
         <v>268</v>
       </c>
@@ -5948,8 +6587,11 @@
       <c r="E213" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="214" spans="1:5">
+      <c r="F213" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6">
       <c r="A214" s="3" t="s">
         <v>283</v>
       </c>
@@ -5965,8 +6607,11 @@
       <c r="E214" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="215" spans="1:5">
+      <c r="F214" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6">
       <c r="A215" s="3" t="s">
         <v>284</v>
       </c>
@@ -5982,8 +6627,11 @@
       <c r="E215" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="216" spans="1:5">
+      <c r="F215" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6">
       <c r="A216" s="3" t="s">
         <v>285</v>
       </c>
@@ -5999,8 +6647,11 @@
       <c r="E216" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="217" spans="1:5">
+      <c r="F216" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6">
       <c r="A217" s="3" t="s">
         <v>286</v>
       </c>
@@ -6016,8 +6667,11 @@
       <c r="E217" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="218" spans="1:5">
+      <c r="F217" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6">
       <c r="A218" s="3" t="s">
         <v>287</v>
       </c>
@@ -6033,8 +6687,11 @@
       <c r="E218" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="219" spans="1:5">
+      <c r="F218" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6">
       <c r="A219" s="3" t="s">
         <v>288</v>
       </c>
@@ -6050,8 +6707,11 @@
       <c r="E219" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="220" spans="1:5">
+      <c r="F219" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6">
       <c r="A220" s="3" t="s">
         <v>289</v>
       </c>
@@ -6067,8 +6727,11 @@
       <c r="E220" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="221" spans="1:5">
+      <c r="F220" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6">
       <c r="A221" s="3" t="s">
         <v>290</v>
       </c>
@@ -6084,8 +6747,11 @@
       <c r="E221" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="222" spans="1:5">
+      <c r="F221" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6">
       <c r="A222" s="3" t="s">
         <v>291</v>
       </c>
@@ -6101,8 +6767,11 @@
       <c r="E222" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="223" spans="1:5">
+      <c r="F222" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6">
       <c r="A223" s="3" t="s">
         <v>292</v>
       </c>
@@ -6118,8 +6787,11 @@
       <c r="E223" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="224" spans="1:5">
+      <c r="F223" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6">
       <c r="A224" s="3" t="s">
         <v>293</v>
       </c>
@@ -6135,8 +6807,11 @@
       <c r="E224" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="225" spans="1:5">
+      <c r="F224" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6">
       <c r="A225" s="3" t="s">
         <v>294</v>
       </c>
@@ -6152,8 +6827,11 @@
       <c r="E225" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="226" spans="1:5">
+      <c r="F225" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6">
       <c r="A226" s="3" t="s">
         <v>295</v>
       </c>
@@ -6169,8 +6847,11 @@
       <c r="E226" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="227" spans="1:5">
+      <c r="F226" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6">
       <c r="A227" s="3" t="s">
         <v>296</v>
       </c>
@@ -6186,8 +6867,11 @@
       <c r="E227" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="228" spans="1:5">
+      <c r="F227" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6">
       <c r="A228" s="3" t="s">
         <v>297</v>
       </c>
@@ -6203,8 +6887,11 @@
       <c r="E228" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="229" spans="1:5">
+      <c r="F228" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6">
       <c r="A229" s="3" t="s">
         <v>298</v>
       </c>
@@ -6220,8 +6907,11 @@
       <c r="E229" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="230" spans="1:5">
+      <c r="F229" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6">
       <c r="A230" s="3" t="s">
         <v>299</v>
       </c>
@@ -6237,8 +6927,11 @@
       <c r="E230" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="231" spans="1:5">
+      <c r="F230" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6">
       <c r="A231" s="3" t="s">
         <v>301</v>
       </c>
@@ -6254,8 +6947,11 @@
       <c r="E231" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="232" spans="1:5">
+      <c r="F231" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6">
       <c r="A232" s="3" t="s">
         <v>302</v>
       </c>
@@ -6271,8 +6967,11 @@
       <c r="E232" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="233" spans="1:5">
+      <c r="F232" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6">
       <c r="A233" s="3" t="s">
         <v>303</v>
       </c>
@@ -6288,8 +6987,11 @@
       <c r="E233" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="234" spans="1:5">
+      <c r="F233" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6">
       <c r="A234" s="3" t="s">
         <v>304</v>
       </c>
@@ -6305,8 +7007,11 @@
       <c r="E234" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="235" spans="1:5">
+      <c r="F234" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6">
       <c r="A235" s="3" t="s">
         <v>305</v>
       </c>
@@ -6322,8 +7027,11 @@
       <c r="E235" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="236" spans="1:5">
+      <c r="F235" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6">
       <c r="A236" s="3" t="s">
         <v>306</v>
       </c>
@@ -6339,8 +7047,11 @@
       <c r="E236" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="237" spans="1:5">
+      <c r="F236" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6">
       <c r="A237" s="3" t="s">
         <v>307</v>
       </c>
@@ -6356,8 +7067,11 @@
       <c r="E237" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="238" spans="1:5">
+      <c r="F237" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6">
       <c r="A238" s="3" t="s">
         <v>308</v>
       </c>
@@ -6373,8 +7087,11 @@
       <c r="E238" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="239" spans="1:5">
+      <c r="F238" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6">
       <c r="A239" s="3" t="s">
         <v>309</v>
       </c>
@@ -6390,8 +7107,11 @@
       <c r="E239" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="240" spans="1:5">
+      <c r="F239" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6">
       <c r="A240" s="3" t="s">
         <v>311</v>
       </c>
@@ -6407,8 +7127,11 @@
       <c r="E240" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="241" spans="1:5">
+      <c r="F240" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6">
       <c r="A241" s="3" t="s">
         <v>312</v>
       </c>
@@ -6424,8 +7147,11 @@
       <c r="E241" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="242" spans="1:5">
+      <c r="F241" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6">
       <c r="A242" s="3" t="s">
         <v>326</v>
       </c>
@@ -6441,8 +7167,11 @@
       <c r="E242" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="243" spans="1:5">
+      <c r="F242" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6">
       <c r="A243" s="3" t="s">
         <v>327</v>
       </c>
@@ -6458,8 +7187,11 @@
       <c r="E243" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="244" spans="1:5">
+      <c r="F243" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6">
       <c r="A244" s="3" t="s">
         <v>328</v>
       </c>
@@ -6475,8 +7207,11 @@
       <c r="E244" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="245" spans="1:5">
+      <c r="F244" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6">
       <c r="A245" s="3" t="s">
         <v>329</v>
       </c>
@@ -6492,8 +7227,11 @@
       <c r="E245" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="246" spans="1:5">
+      <c r="F245" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6">
       <c r="A246" s="3" t="s">
         <v>313</v>
       </c>
@@ -6509,8 +7247,11 @@
       <c r="E246" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="247" spans="1:5">
+      <c r="F246" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6">
       <c r="A247" s="3" t="s">
         <v>314</v>
       </c>
@@ -6526,8 +7267,11 @@
       <c r="E247" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="248" spans="1:5">
+      <c r="F247" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6">
       <c r="A248" s="3" t="s">
         <v>315</v>
       </c>
@@ -6543,8 +7287,11 @@
       <c r="E248" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="249" spans="1:5">
+      <c r="F248" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6">
       <c r="A249" s="3" t="s">
         <v>316</v>
       </c>
@@ -6560,8 +7307,11 @@
       <c r="E249" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="250" spans="1:5">
+      <c r="F249" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6">
       <c r="A250" s="3" t="s">
         <v>317</v>
       </c>
@@ -6577,8 +7327,11 @@
       <c r="E250" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="251" spans="1:5">
+      <c r="F250" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6">
       <c r="A251" s="3" t="s">
         <v>318</v>
       </c>
@@ -6594,8 +7347,11 @@
       <c r="E251" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="252" spans="1:5">
+      <c r="F251" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6">
       <c r="A252" s="3" t="s">
         <v>319</v>
       </c>
@@ -6611,8 +7367,11 @@
       <c r="E252" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="253" spans="1:5">
+      <c r="F252" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6">
       <c r="A253" s="3" t="s">
         <v>320</v>
       </c>
@@ -6628,8 +7387,11 @@
       <c r="E253" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="254" spans="1:5">
+      <c r="F253" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6">
       <c r="A254" s="3" t="s">
         <v>321</v>
       </c>
@@ -6645,8 +7407,11 @@
       <c r="E254" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="255" spans="1:5">
+      <c r="F254" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6">
       <c r="A255" s="3" t="s">
         <v>323</v>
       </c>
@@ -6662,8 +7427,11 @@
       <c r="E255" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="256" spans="1:5">
+      <c r="F255" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6">
       <c r="A256" s="3" t="s">
         <v>324</v>
       </c>
@@ -6679,8 +7447,11 @@
       <c r="E256" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="257" spans="1:5">
+      <c r="F256" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6">
       <c r="A257" s="3" t="s">
         <v>325</v>
       </c>
@@ -6696,8 +7467,11 @@
       <c r="E257" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="258" spans="1:5">
+      <c r="F257" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6">
       <c r="A258" s="3" t="s">
         <v>327</v>
       </c>
@@ -6713,8 +7487,11 @@
       <c r="E258" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="259" spans="1:5">
+      <c r="F258" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6">
       <c r="A259" s="3" t="s">
         <v>330</v>
       </c>
@@ -6730,8 +7507,11 @@
       <c r="E259" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="260" spans="1:5">
+      <c r="F259" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6">
       <c r="A260" s="3" t="s">
         <v>322</v>
       </c>
@@ -6747,8 +7527,11 @@
       <c r="E260" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="261" spans="1:5">
+      <c r="F260" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6">
       <c r="A261" s="3" t="s">
         <v>331</v>
       </c>
@@ -6764,8 +7547,11 @@
       <c r="E261" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="262" spans="1:5">
+      <c r="F261" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
       <c r="A262" s="3" t="s">
         <v>333</v>
       </c>
@@ -6781,8 +7567,11 @@
       <c r="E262" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="263" spans="1:5">
+      <c r="F262" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
       <c r="A263" s="3" t="s">
         <v>334</v>
       </c>
@@ -6798,8 +7587,11 @@
       <c r="E263" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="264" spans="1:5">
+      <c r="F263" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
       <c r="A264" s="3" t="s">
         <v>335</v>
       </c>
@@ -6815,8 +7607,11 @@
       <c r="E264" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="265" spans="1:5">
+      <c r="F264" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
       <c r="A265" s="3" t="s">
         <v>336</v>
       </c>
@@ -6832,8 +7627,11 @@
       <c r="E265" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="266" spans="1:5">
+      <c r="F265" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
       <c r="A266" s="3" t="s">
         <v>337</v>
       </c>
@@ -6849,8 +7647,11 @@
       <c r="E266" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="267" spans="1:5">
+      <c r="F266" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
       <c r="A267" s="3" t="s">
         <v>338</v>
       </c>
@@ -6866,8 +7667,11 @@
       <c r="E267" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="268" spans="1:5">
+      <c r="F267" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
       <c r="A268" s="3" t="s">
         <v>339</v>
       </c>
@@ -6883,8 +7687,11 @@
       <c r="E268" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="269" spans="1:5">
+      <c r="F268" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
       <c r="A269" s="3" t="s">
         <v>340</v>
       </c>
@@ -6900,8 +7707,11 @@
       <c r="E269" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="270" spans="1:5">
+      <c r="F269" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
       <c r="A270" s="3" t="s">
         <v>341</v>
       </c>
@@ -6917,8 +7727,11 @@
       <c r="E270" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="271" spans="1:5">
+      <c r="F270" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
       <c r="A271" s="3" t="s">
         <v>342</v>
       </c>
@@ -6934,8 +7747,11 @@
       <c r="E271" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="272" spans="1:5">
+      <c r="F271" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
       <c r="A272" s="3" t="s">
         <v>343</v>
       </c>
@@ -6951,8 +7767,11 @@
       <c r="E272" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="273" spans="1:5">
+      <c r="F272" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
       <c r="A273" s="3" t="s">
         <v>344</v>
       </c>
@@ -6968,8 +7787,11 @@
       <c r="E273" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="274" spans="1:5">
+      <c r="F273" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
       <c r="A274" s="3" t="s">
         <v>345</v>
       </c>
@@ -6985,8 +7807,11 @@
       <c r="E274" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="275" spans="1:5">
+      <c r="F274" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
       <c r="A275" s="3" t="s">
         <v>346</v>
       </c>
@@ -7002,8 +7827,11 @@
       <c r="E275" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="276" spans="1:5">
+      <c r="F275" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
       <c r="A276" s="3" t="s">
         <v>347</v>
       </c>
@@ -7019,8 +7847,11 @@
       <c r="E276" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="277" spans="1:5">
+      <c r="F276" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
       <c r="A277" s="3" t="s">
         <v>348</v>
       </c>
@@ -7036,8 +7867,11 @@
       <c r="E277" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="278" spans="1:5">
+      <c r="F277" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
       <c r="A278" s="3" t="s">
         <v>352</v>
       </c>
@@ -7053,8 +7887,11 @@
       <c r="E278" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="279" spans="1:5">
+      <c r="F278" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
       <c r="A279" s="3" t="s">
         <v>353</v>
       </c>
@@ -7070,8 +7907,11 @@
       <c r="E279" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="280" spans="1:5">
+      <c r="F279" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
       <c r="A280" s="3" t="s">
         <v>356</v>
       </c>
@@ -7087,8 +7927,11 @@
       <c r="E280" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="281" spans="1:5">
+      <c r="F280" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
       <c r="A281" s="3" t="s">
         <v>357</v>
       </c>
@@ -7104,8 +7947,11 @@
       <c r="E281" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="282" spans="1:5">
+      <c r="F281" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
       <c r="A282" s="3" t="s">
         <v>358</v>
       </c>
@@ -7121,8 +7967,11 @@
       <c r="E282" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="283" spans="1:5">
+      <c r="F282" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
       <c r="A283" s="3" t="s">
         <v>359</v>
       </c>
@@ -7138,8 +7987,11 @@
       <c r="E283" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="284" spans="1:5">
+      <c r="F283" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
       <c r="A284" s="3" t="s">
         <v>352</v>
       </c>
@@ -7155,8 +8007,11 @@
       <c r="E284" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="285" spans="1:5">
+      <c r="F284" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
       <c r="A285" s="3" t="s">
         <v>353</v>
       </c>
@@ -7172,8 +8027,11 @@
       <c r="E285" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="286" spans="1:5">
+      <c r="F285" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
       <c r="A286" s="3" t="s">
         <v>354</v>
       </c>
@@ -7189,8 +8047,11 @@
       <c r="E286" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="287" spans="1:5">
+      <c r="F286" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
       <c r="A287" s="3" t="s">
         <v>355</v>
       </c>
@@ -7206,8 +8067,11 @@
       <c r="E287" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="288" spans="1:5">
+      <c r="F287" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
       <c r="A288" s="3" t="s">
         <v>360</v>
       </c>
@@ -7223,8 +8087,11 @@
       <c r="E288" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="289" spans="1:5">
+      <c r="F288" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
       <c r="A289" s="3" t="s">
         <v>362</v>
       </c>
@@ -7240,8 +8107,11 @@
       <c r="E289" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="290" spans="1:5">
+      <c r="F289" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
       <c r="A290" s="3" t="s">
         <v>69</v>
       </c>
@@ -7257,8 +8127,11 @@
       <c r="E290" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="291" spans="1:5">
+      <c r="F290" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
       <c r="A291" s="3" t="s">
         <v>365</v>
       </c>
@@ -7274,8 +8147,11 @@
       <c r="E291" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="292" spans="1:5">
+      <c r="F291" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
       <c r="A292" s="3" t="s">
         <v>366</v>
       </c>
@@ -7291,8 +8167,11 @@
       <c r="E292" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="293" spans="1:5">
+      <c r="F292" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
       <c r="A293" s="3" t="s">
         <v>367</v>
       </c>
@@ -7308,8 +8187,11 @@
       <c r="E293" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="294" spans="1:5">
+      <c r="F293" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
       <c r="A294" s="3" t="s">
         <v>374</v>
       </c>
@@ -7325,8 +8207,11 @@
       <c r="E294" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="295" spans="1:5">
+      <c r="F294" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
       <c r="A295" s="3" t="s">
         <v>375</v>
       </c>
@@ -7342,8 +8227,11 @@
       <c r="E295" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="296" spans="1:5">
+      <c r="F295" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
       <c r="A296" s="3" t="s">
         <v>376</v>
       </c>
@@ -7359,8 +8247,11 @@
       <c r="E296" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="297" spans="1:5">
+      <c r="F296" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
       <c r="A297" s="3" t="s">
         <v>377</v>
       </c>
@@ -7376,8 +8267,11 @@
       <c r="E297" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="298" spans="1:5">
+      <c r="F297" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
       <c r="A298" s="3" t="s">
         <v>378</v>
       </c>
@@ -7393,8 +8287,11 @@
       <c r="E298" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="299" spans="1:5">
+      <c r="F298" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
       <c r="A299" s="3" t="s">
         <v>379</v>
       </c>
@@ -7410,8 +8307,11 @@
       <c r="E299" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="300" spans="1:5">
+      <c r="F299" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
       <c r="A300" s="3" t="s">
         <v>380</v>
       </c>
@@ -7427,8 +8327,11 @@
       <c r="E300" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="301" spans="1:5">
+      <c r="F300" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
       <c r="A301" s="3" t="s">
         <v>381</v>
       </c>
@@ -7444,8 +8347,11 @@
       <c r="E301" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="302" spans="1:5">
+      <c r="F301" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
       <c r="A302" s="3" t="s">
         <v>382</v>
       </c>
@@ -7461,8 +8367,11 @@
       <c r="E302" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="303" spans="1:5">
+      <c r="F302" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
       <c r="A303" s="3" t="s">
         <v>383</v>
       </c>
@@ -7478,8 +8387,11 @@
       <c r="E303" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="304" spans="1:5">
+      <c r="F303" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
       <c r="A304" s="3" t="s">
         <v>384</v>
       </c>
@@ -7495,8 +8407,11 @@
       <c r="E304" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="305" spans="1:5">
+      <c r="F304" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
       <c r="A305" s="3" t="s">
         <v>374</v>
       </c>
@@ -7512,8 +8427,11 @@
       <c r="E305" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="306" spans="1:5">
+      <c r="F305" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
       <c r="A306" s="3" t="s">
         <v>375</v>
       </c>
@@ -7529,8 +8447,11 @@
       <c r="E306" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="307" spans="1:5">
+      <c r="F306" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
       <c r="A307" s="3" t="s">
         <v>378</v>
       </c>
@@ -7546,8 +8467,11 @@
       <c r="E307" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="308" spans="1:5">
+      <c r="F307" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
       <c r="A308" s="3" t="s">
         <v>385</v>
       </c>
@@ -7563,8 +8487,11 @@
       <c r="E308" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="309" spans="1:5">
+      <c r="F308" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
       <c r="A309" s="3" t="s">
         <v>386</v>
       </c>
@@ -7580,8 +8507,11 @@
       <c r="E309" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="310" spans="1:5">
+      <c r="F309" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
       <c r="A310" s="3" t="s">
         <v>387</v>
       </c>
@@ -7597,8 +8527,11 @@
       <c r="E310" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="311" spans="1:5">
+      <c r="F310" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
       <c r="A311" s="3" t="s">
         <v>388</v>
       </c>
@@ -7614,8 +8547,11 @@
       <c r="E311" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="312" spans="1:5">
+      <c r="F311" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
       <c r="A312" s="3" t="s">
         <v>389</v>
       </c>
@@ -7631,8 +8567,11 @@
       <c r="E312" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="313" spans="1:5">
+      <c r="F312" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
       <c r="A313" s="3" t="s">
         <v>390</v>
       </c>
@@ -7648,8 +8587,11 @@
       <c r="E313" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="314" spans="1:5">
+      <c r="F313" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6">
       <c r="A314" s="3" t="s">
         <v>391</v>
       </c>
@@ -7665,8 +8607,11 @@
       <c r="E314" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="315" spans="1:5">
+      <c r="F314" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6">
       <c r="A315" s="3" t="s">
         <v>392</v>
       </c>
@@ -7682,8 +8627,11 @@
       <c r="E315" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="316" spans="1:5">
+      <c r="F315" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6">
       <c r="A316" s="3" t="s">
         <v>393</v>
       </c>
@@ -7699,8 +8647,11 @@
       <c r="E316" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="317" spans="1:5">
+      <c r="F316" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6">
       <c r="A317" s="3" t="s">
         <v>394</v>
       </c>
@@ -7716,8 +8667,11 @@
       <c r="E317" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="318" spans="1:5">
+      <c r="F317" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6">
       <c r="A318" s="3" t="s">
         <v>395</v>
       </c>
@@ -7733,8 +8687,11 @@
       <c r="E318" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="319" spans="1:5">
+      <c r="F318" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6">
       <c r="A319" s="3" t="s">
         <v>396</v>
       </c>
@@ -7750,8 +8707,11 @@
       <c r="E319" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="320" spans="1:5">
+      <c r="F319" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6">
       <c r="A320" s="3" t="s">
         <v>397</v>
       </c>
@@ -7767,8 +8727,11 @@
       <c r="E320" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="321" spans="1:5">
+      <c r="F320" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6">
       <c r="A321" s="3" t="s">
         <v>398</v>
       </c>
@@ -7784,8 +8747,11 @@
       <c r="E321" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="322" spans="1:5">
+      <c r="F321" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6">
       <c r="A322" s="3" t="s">
         <v>399</v>
       </c>
@@ -7801,8 +8767,11 @@
       <c r="E322" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="323" spans="1:5">
+      <c r="F322" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6">
       <c r="A323" s="3" t="s">
         <v>400</v>
       </c>
@@ -7818,8 +8787,11 @@
       <c r="E323" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="324" spans="1:5">
+      <c r="F323" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6">
       <c r="A324" s="3" t="s">
         <v>403</v>
       </c>
@@ -7835,8 +8807,11 @@
       <c r="E324" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="325" spans="1:5">
+      <c r="F324" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6">
       <c r="A325" s="3" t="s">
         <v>409</v>
       </c>
@@ -7852,8 +8827,11 @@
       <c r="E325" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="326" spans="1:5">
+      <c r="F325" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="326" spans="1:6">
       <c r="A326" s="3" t="s">
         <v>410</v>
       </c>
@@ -7869,8 +8847,11 @@
       <c r="E326" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="327" spans="1:5">
+      <c r="F326" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="327" spans="1:6">
       <c r="A327" s="3" t="s">
         <v>413</v>
       </c>
@@ -7886,8 +8867,11 @@
       <c r="E327" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="328" spans="1:5">
+      <c r="F327" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="328" spans="1:6">
       <c r="A328" s="3" t="s">
         <v>417</v>
       </c>
@@ -7903,8 +8887,11 @@
       <c r="E328" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="329" spans="1:5">
+      <c r="F328" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="329" spans="1:6">
       <c r="A329" s="3" t="s">
         <v>418</v>
       </c>
@@ -7920,8 +8907,11 @@
       <c r="E329" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="330" spans="1:5">
+      <c r="F329" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="330" spans="1:6">
       <c r="A330" s="3" t="s">
         <v>420</v>
       </c>
@@ -7937,8 +8927,11 @@
       <c r="E330" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="331" spans="1:5">
+      <c r="F330" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="331" spans="1:6">
       <c r="A331" s="3" t="s">
         <v>421</v>
       </c>
@@ -7954,8 +8947,11 @@
       <c r="E331" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="332" spans="1:5">
+      <c r="F331" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="332" spans="1:6">
       <c r="A332" s="3" t="s">
         <v>422</v>
       </c>
@@ -7971,8 +8967,11 @@
       <c r="E332" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="333" spans="1:5">
+      <c r="F332" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="333" spans="1:6">
       <c r="A333" s="3" t="s">
         <v>423</v>
       </c>
@@ -7988,8 +8987,11 @@
       <c r="E333" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="334" spans="1:5">
+      <c r="F333" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="334" spans="1:6">
       <c r="A334" s="3" t="s">
         <v>50</v>
       </c>
@@ -8005,8 +9007,11 @@
       <c r="E334" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="335" spans="1:5">
+      <c r="F334" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="335" spans="1:6">
       <c r="A335" s="3" t="s">
         <v>424</v>
       </c>
@@ -8022,8 +9027,11 @@
       <c r="E335" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="336" spans="1:5">
+      <c r="F335" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="336" spans="1:6">
       <c r="A336" s="3" t="s">
         <v>425</v>
       </c>
@@ -8039,8 +9047,11 @@
       <c r="E336" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="337" spans="1:5">
+      <c r="F336" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="337" spans="1:6">
       <c r="A337" s="3" t="s">
         <v>426</v>
       </c>
@@ -8056,8 +9067,11 @@
       <c r="E337" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="338" spans="1:5">
+      <c r="F337" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="338" spans="1:6">
       <c r="A338" s="3" t="s">
         <v>427</v>
       </c>
@@ -8073,8 +9087,11 @@
       <c r="E338" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="339" spans="1:5">
+      <c r="F338" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="339" spans="1:6">
       <c r="A339" s="3" t="s">
         <v>428</v>
       </c>
@@ -8090,8 +9107,11 @@
       <c r="E339" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="340" spans="1:5">
+      <c r="F339" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="340" spans="1:6">
       <c r="A340" s="3" t="s">
         <v>429</v>
       </c>
@@ -8107,8 +9127,11 @@
       <c r="E340" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="341" spans="1:5">
+      <c r="F340" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="341" spans="1:6">
       <c r="A341" s="3" t="s">
         <v>349</v>
       </c>
@@ -8124,8 +9147,11 @@
       <c r="E341" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="342" spans="1:5">
+      <c r="F341" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="342" spans="1:6">
       <c r="A342" s="3" t="s">
         <v>350</v>
       </c>
@@ -8141,8 +9167,11 @@
       <c r="E342" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="343" spans="1:5">
+      <c r="F342" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="343" spans="1:6">
       <c r="A343" s="3" t="s">
         <v>432</v>
       </c>
@@ -8158,8 +9187,11 @@
       <c r="E343" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="344" spans="1:5">
+      <c r="F343" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="344" spans="1:6">
       <c r="A344" s="3" t="s">
         <v>433</v>
       </c>
@@ -8175,8 +9207,11 @@
       <c r="E344" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="345" spans="1:5">
+      <c r="F344" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="345" spans="1:6">
       <c r="A345" s="3" t="s">
         <v>434</v>
       </c>
@@ -8192,8 +9227,11 @@
       <c r="E345" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="346" spans="1:5">
+      <c r="F345" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="346" spans="1:6">
       <c r="A346" s="3" t="s">
         <v>435</v>
       </c>
@@ -8209,8 +9247,11 @@
       <c r="E346" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="347" spans="1:5">
+      <c r="F346" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="347" spans="1:6">
       <c r="A347" s="3" t="s">
         <v>436</v>
       </c>
@@ -8226,8 +9267,11 @@
       <c r="E347" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="348" spans="1:5">
+      <c r="F347" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="348" spans="1:6">
       <c r="A348" s="3" t="s">
         <v>438</v>
       </c>
@@ -8243,8 +9287,11 @@
       <c r="E348" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="349" spans="1:5">
+      <c r="F348" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="349" spans="1:6">
       <c r="A349" s="3" t="s">
         <v>56</v>
       </c>
@@ -8260,8 +9307,11 @@
       <c r="E349" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="350" spans="1:5">
+      <c r="F349" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="350" spans="1:6">
       <c r="A350" s="3" t="s">
         <v>271</v>
       </c>
@@ -8277,8 +9327,11 @@
       <c r="E350" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="351" spans="1:5">
+      <c r="F350" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="351" spans="1:6">
       <c r="A351" s="3" t="s">
         <v>272</v>
       </c>
@@ -8294,8 +9347,11 @@
       <c r="E351" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="352" spans="1:5">
+      <c r="F351" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="352" spans="1:6">
       <c r="A352" s="3" t="s">
         <v>273</v>
       </c>
@@ -8311,8 +9367,11 @@
       <c r="E352" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="353" spans="1:5">
+      <c r="F352" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="353" spans="1:6">
       <c r="A353" s="3" t="s">
         <v>274</v>
       </c>
@@ -8328,8 +9387,11 @@
       <c r="E353" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="354" spans="1:5">
+      <c r="F353" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="354" spans="1:6">
       <c r="A354" s="3" t="s">
         <v>275</v>
       </c>
@@ -8345,8 +9407,11 @@
       <c r="E354" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="355" spans="1:5">
+      <c r="F354" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="355" spans="1:6">
       <c r="A355" s="3" t="s">
         <v>276</v>
       </c>
@@ -8362,8 +9427,11 @@
       <c r="E355" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="356" spans="1:5">
+      <c r="F355" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="356" spans="1:6">
       <c r="A356" s="3" t="s">
         <v>277</v>
       </c>
@@ -8379,8 +9447,11 @@
       <c r="E356" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="357" spans="1:5">
+      <c r="F356" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="357" spans="1:6">
       <c r="A357" s="3" t="s">
         <v>278</v>
       </c>
@@ -8396,8 +9467,11 @@
       <c r="E357" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="358" spans="1:5">
+      <c r="F357" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="358" spans="1:6">
       <c r="A358" s="3" t="s">
         <v>279</v>
       </c>
@@ -8413,8 +9487,11 @@
       <c r="E358" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="359" spans="1:5">
+      <c r="F358" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="359" spans="1:6">
       <c r="A359" s="3" t="s">
         <v>281</v>
       </c>
@@ -8430,8 +9507,11 @@
       <c r="E359" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="360" spans="1:5">
+      <c r="F359" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="360" spans="1:6">
       <c r="A360" s="3" t="s">
         <v>282</v>
       </c>
@@ -8447,8 +9527,11 @@
       <c r="E360" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="361" spans="1:5">
+      <c r="F360" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="361" spans="1:6">
       <c r="A361" s="3" t="s">
         <v>280</v>
       </c>
@@ -8464,8 +9547,11 @@
       <c r="E361" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="362" spans="1:5">
+      <c r="F361" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="362" spans="1:6">
       <c r="A362" s="3" t="s">
         <v>439</v>
       </c>
@@ -8481,8 +9567,11 @@
       <c r="E362" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="363" spans="1:5">
+      <c r="F362" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="363" spans="1:6">
       <c r="A363" s="3" t="s">
         <v>440</v>
       </c>
@@ -8498,8 +9587,11 @@
       <c r="E363" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="364" spans="1:5">
+      <c r="F363" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="364" spans="1:6">
       <c r="A364" s="3" t="s">
         <v>441</v>
       </c>
@@ -8515,8 +9607,11 @@
       <c r="E364" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="365" spans="1:5">
+      <c r="F364" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="365" spans="1:6">
       <c r="A365" s="3" t="s">
         <v>442</v>
       </c>
@@ -8532,8 +9627,11 @@
       <c r="E365" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="366" spans="1:5">
+      <c r="F365" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="366" spans="1:6">
       <c r="A366" s="3" t="s">
         <v>443</v>
       </c>
@@ -8549,8 +9647,11 @@
       <c r="E366" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="367" spans="1:5">
+      <c r="F366" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="367" spans="1:6">
       <c r="A367" s="3" t="s">
         <v>444</v>
       </c>
@@ -8566,8 +9667,11 @@
       <c r="E367" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="368" spans="1:5">
+      <c r="F367" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="368" spans="1:6">
       <c r="A368" s="3" t="s">
         <v>445</v>
       </c>
@@ -8583,8 +9687,11 @@
       <c r="E368" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="369" spans="1:5">
+      <c r="F368" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="369" spans="1:6">
       <c r="A369" s="3" t="s">
         <v>446</v>
       </c>
@@ -8600,8 +9707,11 @@
       <c r="E369" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="370" spans="1:5">
+      <c r="F369" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="370" spans="1:6">
       <c r="A370" s="3" t="s">
         <v>447</v>
       </c>
@@ -8617,8 +9727,11 @@
       <c r="E370" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="371" spans="1:5">
+      <c r="F370" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="371" spans="1:6">
       <c r="A371" s="3" t="s">
         <v>448</v>
       </c>
@@ -8634,8 +9747,11 @@
       <c r="E371" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="372" spans="1:5">
+      <c r="F371" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="372" spans="1:6">
       <c r="A372" s="3" t="s">
         <v>449</v>
       </c>
@@ -8651,8 +9767,11 @@
       <c r="E372" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="373" spans="1:5">
+      <c r="F372" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="373" spans="1:6">
       <c r="A373" s="3" t="s">
         <v>450</v>
       </c>
@@ -8668,8 +9787,11 @@
       <c r="E373" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="374" spans="1:5">
+      <c r="F373" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="374" spans="1:6">
       <c r="A374" s="3" t="s">
         <v>451</v>
       </c>
@@ -8685,8 +9807,11 @@
       <c r="E374" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="375" spans="1:5">
+      <c r="F374" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="375" spans="1:6">
       <c r="A375" s="3" t="s">
         <v>452</v>
       </c>
@@ -8702,8 +9827,11 @@
       <c r="E375" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="376" spans="1:5">
+      <c r="F375" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="376" spans="1:6">
       <c r="A376" s="3" t="s">
         <v>453</v>
       </c>
@@ -8719,8 +9847,11 @@
       <c r="E376" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="377" spans="1:5">
+      <c r="F376" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="377" spans="1:6">
       <c r="A377" s="3" t="s">
         <v>454</v>
       </c>
@@ -8736,8 +9867,11 @@
       <c r="E377" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="378" spans="1:5">
+      <c r="F377" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="378" spans="1:6">
       <c r="A378" s="3" t="s">
         <v>455</v>
       </c>
@@ -8753,8 +9887,11 @@
       <c r="E378" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="379" spans="1:5">
+      <c r="F378" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="379" spans="1:6">
       <c r="A379" s="3" t="s">
         <v>460</v>
       </c>
@@ -8770,8 +9907,11 @@
       <c r="E379" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="380" spans="1:5">
+      <c r="F379" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="380" spans="1:6">
       <c r="A380" s="3" t="s">
         <v>461</v>
       </c>
@@ -8787,8 +9927,11 @@
       <c r="E380" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="381" spans="1:5">
+      <c r="F380" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="381" spans="1:6">
       <c r="A381" s="3" t="s">
         <v>462</v>
       </c>
@@ -8804,8 +9947,11 @@
       <c r="E381" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="382" spans="1:5">
+      <c r="F381" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="382" spans="1:6">
       <c r="A382" s="3" t="s">
         <v>463</v>
       </c>
@@ -8821,8 +9967,11 @@
       <c r="E382" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="383" spans="1:5">
+      <c r="F382" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="383" spans="1:6">
       <c r="A383" s="3" t="s">
         <v>465</v>
       </c>
@@ -8838,8 +9987,11 @@
       <c r="E383" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="384" spans="1:5">
+      <c r="F383" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="384" spans="1:6">
       <c r="A384" s="3" t="s">
         <v>466</v>
       </c>
@@ -8855,8 +10007,11 @@
       <c r="E384" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="385" spans="1:5">
+      <c r="F384" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="385" spans="1:6">
       <c r="A385" s="3" t="s">
         <v>467</v>
       </c>
@@ -8872,8 +10027,11 @@
       <c r="E385" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="386" spans="1:5">
+      <c r="F385" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="386" spans="1:6">
       <c r="A386" s="3" t="s">
         <v>468</v>
       </c>
@@ -8889,8 +10047,11 @@
       <c r="E386" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="387" spans="1:5">
+      <c r="F386" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="387" spans="1:6">
       <c r="A387" s="3" t="s">
         <v>469</v>
       </c>
@@ -8906,8 +10067,11 @@
       <c r="E387" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="388" spans="1:5">
+      <c r="F387" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="388" spans="1:6">
       <c r="A388" s="3" t="s">
         <v>472</v>
       </c>
@@ -8923,8 +10087,11 @@
       <c r="E388" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="389" spans="1:5">
+      <c r="F388" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="389" spans="1:6">
       <c r="A389" s="3" t="s">
         <v>369</v>
       </c>
@@ -8940,8 +10107,11 @@
       <c r="E389" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="390" spans="1:5">
+      <c r="F389" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="390" spans="1:6">
       <c r="A390" s="3" t="s">
         <v>473</v>
       </c>
@@ -8957,8 +10127,11 @@
       <c r="E390" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="391" spans="1:5">
+      <c r="F390" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="391" spans="1:6">
       <c r="A391" s="3" t="s">
         <v>474</v>
       </c>
@@ -8974,8 +10147,11 @@
       <c r="E391" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="392" spans="1:5">
+      <c r="F391" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="392" spans="1:6">
       <c r="A392" s="3" t="s">
         <v>475</v>
       </c>
@@ -8991,8 +10167,11 @@
       <c r="E392" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="393" spans="1:5">
+      <c r="F392" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="393" spans="1:6">
       <c r="A393" s="3" t="s">
         <v>476</v>
       </c>
@@ -9008,8 +10187,11 @@
       <c r="E393" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="394" spans="1:5">
+      <c r="F393" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="394" spans="1:6">
       <c r="A394" s="3" t="s">
         <v>477</v>
       </c>
@@ -9025,8 +10207,11 @@
       <c r="E394" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="395" spans="1:5">
+      <c r="F394" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="395" spans="1:6">
       <c r="A395" s="3" t="s">
         <v>478</v>
       </c>
@@ -9042,8 +10227,11 @@
       <c r="E395" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="396" spans="1:5">
+      <c r="F395" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="396" spans="1:6">
       <c r="A396" s="3" t="s">
         <v>479</v>
       </c>
@@ -9059,8 +10247,11 @@
       <c r="E396" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="397" spans="1:5">
+      <c r="F396" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="397" spans="1:6">
       <c r="A397" s="3" t="s">
         <v>480</v>
       </c>
@@ -9076,8 +10267,11 @@
       <c r="E397" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="398" spans="1:5">
+      <c r="F397" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="398" spans="1:6">
       <c r="A398" s="3" t="s">
         <v>481</v>
       </c>
@@ -9093,8 +10287,11 @@
       <c r="E398" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="399" spans="1:5">
+      <c r="F398" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="399" spans="1:6">
       <c r="A399" s="3" t="s">
         <v>482</v>
       </c>
@@ -9110,8 +10307,11 @@
       <c r="E399" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="400" spans="1:5">
+      <c r="F399" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="400" spans="1:6">
       <c r="A400" s="3" t="s">
         <v>484</v>
       </c>
@@ -9127,8 +10327,11 @@
       <c r="E400" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="401" spans="1:5">
+      <c r="F400" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="401" spans="1:6">
       <c r="A401" s="3" t="s">
         <v>483</v>
       </c>
@@ -9144,8 +10347,11 @@
       <c r="E401" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="402" spans="1:5">
+      <c r="F401" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="402" spans="1:6">
       <c r="A402" s="3" t="s">
         <v>485</v>
       </c>
@@ -9161,8 +10367,11 @@
       <c r="E402" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="403" spans="1:5">
+      <c r="F402" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="403" spans="1:6">
       <c r="A403" s="3" t="s">
         <v>486</v>
       </c>
@@ -9178,8 +10387,11 @@
       <c r="E403" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="404" spans="1:5">
+      <c r="F403" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="404" spans="1:6">
       <c r="A404" s="3" t="s">
         <v>487</v>
       </c>
@@ -9195,8 +10407,11 @@
       <c r="E404" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="405" spans="1:5">
+      <c r="F404" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="405" spans="1:6">
       <c r="A405" s="3" t="s">
         <v>488</v>
       </c>
@@ -9212,8 +10427,11 @@
       <c r="E405" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="406" spans="1:5">
+      <c r="F405" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="406" spans="1:6">
       <c r="A406" s="3" t="s">
         <v>489</v>
       </c>
@@ -9229,8 +10447,11 @@
       <c r="E406" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="407" spans="1:5">
+      <c r="F406" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="407" spans="1:6">
       <c r="A407" s="3" t="s">
         <v>490</v>
       </c>
@@ -9246,8 +10467,11 @@
       <c r="E407" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="408" spans="1:5">
+      <c r="F407" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="408" spans="1:6">
       <c r="A408" s="3" t="s">
         <v>491</v>
       </c>
@@ -9263,8 +10487,11 @@
       <c r="E408" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="409" spans="1:5">
+      <c r="F408" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="409" spans="1:6">
       <c r="A409" s="3" t="s">
         <v>492</v>
       </c>
@@ -9280,8 +10507,11 @@
       <c r="E409" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="410" spans="1:5">
+      <c r="F409" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="410" spans="1:6">
       <c r="A410" s="3" t="s">
         <v>493</v>
       </c>
@@ -9297,8 +10527,11 @@
       <c r="E410" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="411" spans="1:5">
+      <c r="F410" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="411" spans="1:6">
       <c r="A411" s="3" t="s">
         <v>494</v>
       </c>
@@ -9314,8 +10547,11 @@
       <c r="E411" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="412" spans="1:5">
+      <c r="F411" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="412" spans="1:6">
       <c r="A412" s="3" t="s">
         <v>495</v>
       </c>
@@ -9331,8 +10567,11 @@
       <c r="E412" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="413" spans="1:5">
+      <c r="F412" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="413" spans="1:6">
       <c r="A413" s="3" t="s">
         <v>496</v>
       </c>
@@ -9348,8 +10587,11 @@
       <c r="E413" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="414" spans="1:5">
+      <c r="F413" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="414" spans="1:6">
       <c r="A414" s="3" t="s">
         <v>497</v>
       </c>
@@ -9365,8 +10607,11 @@
       <c r="E414" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="415" spans="1:5">
+      <c r="F414" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="415" spans="1:6">
       <c r="A415" s="3" t="s">
         <v>498</v>
       </c>
@@ -9382,8 +10627,11 @@
       <c r="E415" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="416" spans="1:5">
+      <c r="F415" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="416" spans="1:6">
       <c r="A416" s="3" t="s">
         <v>499</v>
       </c>
@@ -9399,8 +10647,11 @@
       <c r="E416" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="417" spans="1:5">
+      <c r="F416" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="417" spans="1:6">
       <c r="A417" s="3" t="s">
         <v>500</v>
       </c>
@@ -9416,8 +10667,11 @@
       <c r="E417" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="418" spans="1:5">
+      <c r="F417" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="418" spans="1:6">
       <c r="A418" s="3" t="s">
         <v>501</v>
       </c>
@@ -9433,8 +10687,11 @@
       <c r="E418" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="419" spans="1:5">
+      <c r="F418" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="419" spans="1:6">
       <c r="A419" s="3" t="s">
         <v>502</v>
       </c>
@@ -9450,8 +10707,11 @@
       <c r="E419" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="420" spans="1:5">
+      <c r="F419" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="420" spans="1:6">
       <c r="A420" s="3" t="s">
         <v>503</v>
       </c>
@@ -9467,8 +10727,11 @@
       <c r="E420" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="421" spans="1:5">
+      <c r="F420" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="421" spans="1:6">
       <c r="A421" s="3" t="s">
         <v>504</v>
       </c>
@@ -9484,8 +10747,11 @@
       <c r="E421" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="422" spans="1:5">
+      <c r="F421" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="422" spans="1:6">
       <c r="A422" s="3" t="s">
         <v>507</v>
       </c>
@@ -9501,8 +10767,11 @@
       <c r="E422" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="423" spans="1:5">
+      <c r="F422" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="423" spans="1:6">
       <c r="A423" s="3" t="s">
         <v>508</v>
       </c>
@@ -9518,8 +10787,11 @@
       <c r="E423" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="424" spans="1:5">
+      <c r="F423" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="424" spans="1:6">
       <c r="A424" s="3" t="s">
         <v>509</v>
       </c>
@@ -9535,8 +10807,11 @@
       <c r="E424" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="425" spans="1:5">
+      <c r="F424" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="425" spans="1:6">
       <c r="A425" s="3" t="s">
         <v>247</v>
       </c>
@@ -9552,8 +10827,11 @@
       <c r="E425" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="426" spans="1:5">
+      <c r="F425" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="426" spans="1:6">
       <c r="A426" s="3" t="s">
         <v>512</v>
       </c>
@@ -9569,8 +10847,11 @@
       <c r="E426" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="427" spans="1:5">
+      <c r="F426" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="427" spans="1:6">
       <c r="A427" s="3" t="s">
         <v>370</v>
       </c>
@@ -9586,8 +10867,11 @@
       <c r="E427" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="428" spans="1:5">
+      <c r="F427" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="428" spans="1:6">
       <c r="A428" s="3" t="s">
         <v>407</v>
       </c>
@@ -9603,8 +10887,11 @@
       <c r="E428" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="429" spans="1:5">
+      <c r="F428" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="429" spans="1:6">
       <c r="A429" s="3" t="s">
         <v>517</v>
       </c>
@@ -9620,8 +10907,11 @@
       <c r="E429" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="430" spans="1:5">
+      <c r="F429" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="430" spans="1:6">
       <c r="A430" s="3" t="s">
         <v>456</v>
       </c>
@@ -9637,8 +10927,11 @@
       <c r="E430" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="431" spans="1:5">
+      <c r="F430" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="431" spans="1:6">
       <c r="A431" s="3" t="s">
         <v>520</v>
       </c>
@@ -9654,8 +10947,11 @@
       <c r="E431" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="432" spans="1:5">
+      <c r="F431" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="432" spans="1:6">
       <c r="A432" s="3" t="s">
         <v>521</v>
       </c>
@@ -9671,8 +10967,11 @@
       <c r="E432" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="433" spans="1:5">
+      <c r="F432" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="433" spans="1:6">
       <c r="A433" s="3" t="s">
         <v>533</v>
       </c>
@@ -9688,8 +10987,11 @@
       <c r="E433" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="434" spans="1:5">
+      <c r="F433" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="434" spans="1:6">
       <c r="A434" s="3" t="s">
         <v>534</v>
       </c>
@@ -9705,8 +11007,11 @@
       <c r="E434" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="435" spans="1:5">
+      <c r="F434" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="435" spans="1:6">
       <c r="A435" s="3" t="s">
         <v>535</v>
       </c>
@@ -9722,8 +11027,11 @@
       <c r="E435" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="436" spans="1:5">
+      <c r="F435" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="436" spans="1:6">
       <c r="A436" s="3" t="s">
         <v>536</v>
       </c>
@@ -9739,8 +11047,11 @@
       <c r="E436" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="437" spans="1:5">
+      <c r="F436" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="437" spans="1:6">
       <c r="A437" s="3" t="s">
         <v>537</v>
       </c>
@@ -9756,8 +11067,11 @@
       <c r="E437" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="438" spans="1:5">
+      <c r="F437" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="438" spans="1:6">
       <c r="A438" s="3" t="s">
         <v>140</v>
       </c>
@@ -9773,8 +11087,11 @@
       <c r="E438" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="439" spans="1:5">
+      <c r="F438" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="439" spans="1:6">
       <c r="A439" s="3" t="s">
         <v>538</v>
       </c>
@@ -9790,8 +11107,11 @@
       <c r="E439" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="440" spans="1:5">
+      <c r="F439" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="440" spans="1:6">
       <c r="A440" s="3" t="s">
         <v>539</v>
       </c>
@@ -9807,8 +11127,11 @@
       <c r="E440" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="441" spans="1:5">
+      <c r="F440" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="441" spans="1:6">
       <c r="A441" s="3" t="s">
         <v>540</v>
       </c>
@@ -9824,8 +11147,11 @@
       <c r="E441" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="442" spans="1:5">
+      <c r="F441" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="442" spans="1:6">
       <c r="A442" s="3" t="s">
         <v>541</v>
       </c>
@@ -9841,8 +11167,11 @@
       <c r="E442" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="443" spans="1:5">
+      <c r="F442" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="443" spans="1:6">
       <c r="A443" s="3" t="s">
         <v>543</v>
       </c>
@@ -9858,8 +11187,11 @@
       <c r="E443" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="444" spans="1:5">
+      <c r="F443" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="444" spans="1:6">
       <c r="A444" s="3" t="s">
         <v>547</v>
       </c>
@@ -9875,8 +11207,11 @@
       <c r="E444" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="445" spans="1:5">
+      <c r="F444" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="445" spans="1:6">
       <c r="A445" s="3" t="s">
         <v>548</v>
       </c>
@@ -9892,8 +11227,11 @@
       <c r="E445" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="446" spans="1:5">
+      <c r="F445" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="446" spans="1:6">
       <c r="A446" s="3" t="s">
         <v>549</v>
       </c>
@@ -9909,8 +11247,11 @@
       <c r="E446" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="447" spans="1:5">
+      <c r="F446" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="447" spans="1:6">
       <c r="A447" s="3" t="s">
         <v>550</v>
       </c>
@@ -9926,8 +11267,11 @@
       <c r="E447" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="448" spans="1:5">
+      <c r="F447" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="448" spans="1:6">
       <c r="A448" s="3" t="s">
         <v>552</v>
       </c>
@@ -9943,8 +11287,11 @@
       <c r="E448" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="449" spans="1:5">
+      <c r="F448" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="449" spans="1:6">
       <c r="A449" s="3" t="s">
         <v>553</v>
       </c>
@@ -9960,8 +11307,11 @@
       <c r="E449" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="450" spans="1:5">
+      <c r="F449" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="450" spans="1:6">
       <c r="A450" s="3" t="s">
         <v>554</v>
       </c>
@@ -9977,8 +11327,11 @@
       <c r="E450" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="451" spans="1:5">
+      <c r="F450" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="451" spans="1:6">
       <c r="A451" s="3" t="s">
         <v>555</v>
       </c>
@@ -9994,8 +11347,11 @@
       <c r="E451" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="452" spans="1:5">
+      <c r="F451" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="452" spans="1:6">
       <c r="A452" s="3" t="s">
         <v>556</v>
       </c>
@@ -10011,8 +11367,11 @@
       <c r="E452" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="453" spans="1:5">
+      <c r="F452" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="453" spans="1:6">
       <c r="A453" s="3" t="s">
         <v>557</v>
       </c>
@@ -10028,8 +11387,11 @@
       <c r="E453" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="454" spans="1:5">
+      <c r="F453" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="454" spans="1:6">
       <c r="A454" s="3" t="s">
         <v>558</v>
       </c>
@@ -10045,8 +11407,11 @@
       <c r="E454" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="455" spans="1:5">
+      <c r="F454" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="455" spans="1:6">
       <c r="A455" s="3" t="s">
         <v>368</v>
       </c>
@@ -10062,8 +11427,11 @@
       <c r="E455" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="456" spans="1:5">
+      <c r="F455" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="456" spans="1:6">
       <c r="A456" s="3" t="s">
         <v>561</v>
       </c>
@@ -10079,8 +11447,11 @@
       <c r="E456" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="457" spans="1:5">
+      <c r="F456" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="457" spans="1:6">
       <c r="A457" s="3" t="s">
         <v>562</v>
       </c>
@@ -10096,8 +11467,11 @@
       <c r="E457" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="458" spans="1:5">
+      <c r="F457" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="458" spans="1:6">
       <c r="A458" s="3" t="s">
         <v>248</v>
       </c>
@@ -10113,8 +11487,11 @@
       <c r="E458" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="459" spans="1:5">
+      <c r="F458" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="459" spans="1:6">
       <c r="A459" s="3" t="s">
         <v>565</v>
       </c>
@@ -10130,8 +11507,11 @@
       <c r="E459" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="460" spans="1:5">
+      <c r="F459" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="460" spans="1:6">
       <c r="A460" s="3" t="s">
         <v>95</v>
       </c>
@@ -10147,8 +11527,11 @@
       <c r="E460" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="461" spans="1:5">
+      <c r="F460" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="461" spans="1:6">
       <c r="A461" s="3" t="s">
         <v>96</v>
       </c>
@@ -10164,8 +11547,11 @@
       <c r="E461" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="462" spans="1:5">
+      <c r="F461" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="462" spans="1:6">
       <c r="A462" s="3" t="s">
         <v>567</v>
       </c>
@@ -10181,8 +11567,11 @@
       <c r="E462" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="463" spans="1:5">
+      <c r="F462" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="463" spans="1:6">
       <c r="A463" s="3" t="s">
         <v>464</v>
       </c>
@@ -10198,8 +11587,11 @@
       <c r="E463" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="464" spans="1:5">
+      <c r="F463" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="464" spans="1:6">
       <c r="A464" s="3" t="s">
         <v>568</v>
       </c>
@@ -10215,8 +11607,11 @@
       <c r="E464" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="465" spans="1:5">
+      <c r="F464" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="465" spans="1:6">
       <c r="A465" s="3" t="s">
         <v>153</v>
       </c>
@@ -10232,8 +11627,11 @@
       <c r="E465" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="466" spans="1:5">
+      <c r="F465" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="466" spans="1:6">
       <c r="A466" s="3" t="s">
         <v>155</v>
       </c>
@@ -10249,8 +11647,11 @@
       <c r="E466" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="467" spans="1:5">
+      <c r="F466" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="467" spans="1:6">
       <c r="A467" s="3" t="s">
         <v>152</v>
       </c>
@@ -10266,8 +11667,11 @@
       <c r="E467" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="468" spans="1:5">
+      <c r="F467" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="468" spans="1:6">
       <c r="A468" s="3" t="s">
         <v>154</v>
       </c>
@@ -10283,8 +11687,11 @@
       <c r="E468" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="469" spans="1:5">
+      <c r="F468" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="469" spans="1:6">
       <c r="A469" s="3" t="s">
         <v>569</v>
       </c>
@@ -10300,8 +11707,11 @@
       <c r="E469" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="470" spans="1:5">
+      <c r="F469" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="470" spans="1:6">
       <c r="A470" s="3" t="s">
         <v>430</v>
       </c>
@@ -10317,8 +11727,11 @@
       <c r="E470" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="471" spans="1:5">
+      <c r="F470" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="471" spans="1:6">
       <c r="A471" s="3" t="s">
         <v>351</v>
       </c>
@@ -10334,8 +11747,11 @@
       <c r="E471" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="472" spans="1:5">
+      <c r="F471" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="472" spans="1:6">
       <c r="A472" s="3" t="s">
         <v>405</v>
       </c>
@@ -10351,8 +11767,11 @@
       <c r="E472" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="473" spans="1:5">
+      <c r="F472" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="473" spans="1:6">
       <c r="A473" s="3" t="s">
         <v>406</v>
       </c>
@@ -10368,8 +11787,11 @@
       <c r="E473" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="474" spans="1:5">
+      <c r="F473" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="474" spans="1:6">
       <c r="A474" s="3" t="s">
         <v>506</v>
       </c>
@@ -10385,8 +11807,11 @@
       <c r="E474" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="475" spans="1:5">
+      <c r="F474" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="475" spans="1:6">
       <c r="A475" s="3" t="s">
         <v>470</v>
       </c>
@@ -10402,8 +11827,11 @@
       <c r="E475" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="476" spans="1:5">
+      <c r="F475" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="476" spans="1:6">
       <c r="A476" s="3" t="s">
         <v>242</v>
       </c>
@@ -10419,8 +11847,11 @@
       <c r="E476" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="477" spans="1:5">
+      <c r="F476" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="477" spans="1:6">
       <c r="A477" s="3" t="s">
         <v>372</v>
       </c>
@@ -10436,8 +11867,11 @@
       <c r="E477" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="478" spans="1:5">
+      <c r="F477" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="478" spans="1:6">
       <c r="A478" s="3" t="s">
         <v>255</v>
       </c>
@@ -10453,8 +11887,11 @@
       <c r="E478" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="479" spans="1:5">
+      <c r="F478" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="479" spans="1:6">
       <c r="A479" s="3" t="s">
         <v>250</v>
       </c>
@@ -10470,8 +11907,11 @@
       <c r="E479" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="480" spans="1:5">
+      <c r="F479" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="480" spans="1:6">
       <c r="A480" s="3" t="s">
         <v>258</v>
       </c>
@@ -10487,8 +11927,11 @@
       <c r="E480" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="481" spans="1:5">
+      <c r="F480" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="481" spans="1:6">
       <c r="A481" s="3" t="s">
         <v>252</v>
       </c>
@@ -10504,8 +11947,11 @@
       <c r="E481" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="482" spans="1:5">
+      <c r="F481" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="482" spans="1:6">
       <c r="A482" s="3" t="s">
         <v>259</v>
       </c>
@@ -10521,8 +11967,11 @@
       <c r="E482" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="483" spans="1:5">
+      <c r="F482" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="483" spans="1:6">
       <c r="A483" s="3" t="s">
         <v>270</v>
       </c>
@@ -10538,8 +11987,11 @@
       <c r="E483" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="484" spans="1:5">
+      <c r="F483" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="484" spans="1:6">
       <c r="A484" s="3" t="s">
         <v>260</v>
       </c>
@@ -10555,8 +12007,11 @@
       <c r="E484" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="485" spans="1:5">
+      <c r="F484" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="485" spans="1:6">
       <c r="A485" s="3" t="s">
         <v>261</v>
       </c>
@@ -10572,8 +12027,11 @@
       <c r="E485" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="486" spans="1:5">
+      <c r="F485" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="486" spans="1:6">
       <c r="A486" s="3" t="s">
         <v>263</v>
       </c>
@@ -10589,8 +12047,11 @@
       <c r="E486" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="487" spans="1:5">
+      <c r="F486" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="487" spans="1:6">
       <c r="A487" s="3" t="s">
         <v>266</v>
       </c>
@@ -10606,8 +12067,11 @@
       <c r="E487" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="488" spans="1:5">
+      <c r="F487" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="488" spans="1:6">
       <c r="A488" s="3" t="s">
         <v>269</v>
       </c>
@@ -10623,8 +12087,11 @@
       <c r="E488" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="489" spans="1:5">
+      <c r="F488" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="489" spans="1:6">
       <c r="A489" s="3" t="s">
         <v>570</v>
       </c>
@@ -10640,8 +12107,11 @@
       <c r="E489" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="490" spans="1:5">
+      <c r="F489" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="490" spans="1:6">
       <c r="A490" s="3" t="s">
         <v>571</v>
       </c>
@@ -10657,8 +12127,11 @@
       <c r="E490" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="491" spans="1:5">
+      <c r="F490" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="491" spans="1:6">
       <c r="A491" s="3" t="s">
         <v>572</v>
       </c>
@@ -10674,8 +12147,11 @@
       <c r="E491" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="492" spans="1:5">
+      <c r="F491" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="492" spans="1:6">
       <c r="A492" s="3" t="s">
         <v>516</v>
       </c>
@@ -10691,8 +12167,11 @@
       <c r="E492" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="493" spans="1:5">
+      <c r="F492" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="493" spans="1:6">
       <c r="A493" s="3" t="s">
         <v>573</v>
       </c>
@@ -10708,8 +12187,11 @@
       <c r="E493" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="494" spans="1:5">
+      <c r="F493" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="494" spans="1:6">
       <c r="A494" s="3" t="s">
         <v>574</v>
       </c>
@@ -10725,8 +12207,11 @@
       <c r="E494" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="495" spans="1:5">
+      <c r="F494" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="495" spans="1:6">
       <c r="A495" s="3" t="s">
         <v>566</v>
       </c>
@@ -10742,8 +12227,11 @@
       <c r="E495" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="496" spans="1:5">
+      <c r="F495" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6">
       <c r="A496" s="3" t="s">
         <v>197</v>
       </c>
@@ -10759,8 +12247,11 @@
       <c r="E496" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="497" spans="1:5">
+      <c r="F496" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
       <c r="A497" s="3" t="s">
         <v>576</v>
       </c>
@@ -10776,8 +12267,11 @@
       <c r="E497" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="498" spans="1:5">
+      <c r="F497" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
       <c r="A498" s="3" t="s">
         <v>577</v>
       </c>
@@ -10793,8 +12287,11 @@
       <c r="E498" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="499" spans="1:5">
+      <c r="F498" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
       <c r="A499" s="3" t="s">
         <v>510</v>
       </c>
@@ -10810,8 +12307,11 @@
       <c r="E499" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="500" spans="1:5">
+      <c r="F499" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
       <c r="A500" s="3" t="s">
         <v>511</v>
       </c>
@@ -10827,8 +12327,11 @@
       <c r="E500" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="501" spans="1:5">
+      <c r="F500" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
       <c r="A501" s="3" t="s">
         <v>579</v>
       </c>
@@ -10844,8 +12347,11 @@
       <c r="E501" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="502" spans="1:5">
+      <c r="F501" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
       <c r="A502" s="3" t="s">
         <v>514</v>
       </c>
@@ -10861,8 +12367,11 @@
       <c r="E502" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="503" spans="1:5">
+      <c r="F502" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
       <c r="A503" s="3" t="s">
         <v>580</v>
       </c>
@@ -10878,8 +12387,11 @@
       <c r="E503" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="504" spans="1:5">
+      <c r="F503" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
       <c r="A504" s="3" t="s">
         <v>581</v>
       </c>
@@ -10895,8 +12407,11 @@
       <c r="E504" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="505" spans="1:5">
+      <c r="F504" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
       <c r="A505" s="3" t="s">
         <v>582</v>
       </c>
@@ -10912,8 +12427,11 @@
       <c r="E505" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="506" spans="1:5">
+      <c r="F505" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
       <c r="A506" s="3" t="s">
         <v>31</v>
       </c>
@@ -10929,8 +12447,11 @@
       <c r="E506" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="507" spans="1:5">
+      <c r="F506" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
       <c r="A507" s="3" t="s">
         <v>148</v>
       </c>
@@ -10946,8 +12467,11 @@
       <c r="E507" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="508" spans="1:5">
+      <c r="F507" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
       <c r="A508" s="3" t="s">
         <v>149</v>
       </c>
@@ -10963,8 +12487,11 @@
       <c r="E508" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="509" spans="1:5">
+      <c r="F508" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
       <c r="A509" s="3" t="s">
         <v>150</v>
       </c>
@@ -10980,8 +12507,11 @@
       <c r="E509" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="510" spans="1:5">
+      <c r="F509" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
       <c r="A510" s="3" t="s">
         <v>151</v>
       </c>
@@ -10997,8 +12527,11 @@
       <c r="E510" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="511" spans="1:5">
+      <c r="F510" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
       <c r="A511" s="3" t="s">
         <v>156</v>
       </c>
@@ -11014,8 +12547,11 @@
       <c r="E511" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="512" spans="1:5">
+      <c r="F511" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
       <c r="A512" s="3" t="s">
         <v>157</v>
       </c>
@@ -11031,8 +12567,11 @@
       <c r="E512" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="513" spans="1:5">
+      <c r="F512" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6">
       <c r="A513" s="3" t="s">
         <v>158</v>
       </c>
@@ -11048,8 +12587,11 @@
       <c r="E513" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="514" spans="1:5">
+      <c r="F513" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6">
       <c r="A514" s="3" t="s">
         <v>165</v>
       </c>
@@ -11065,8 +12607,11 @@
       <c r="E514" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="515" spans="1:5">
+      <c r="F514" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6">
       <c r="A515" s="3" t="s">
         <v>159</v>
       </c>
@@ -11082,8 +12627,11 @@
       <c r="E515" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="516" spans="1:5">
+      <c r="F515" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6">
       <c r="A516" s="3" t="s">
         <v>160</v>
       </c>
@@ -11099,8 +12647,11 @@
       <c r="E516" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="517" spans="1:5">
+      <c r="F516" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6">
       <c r="A517" s="3" t="s">
         <v>161</v>
       </c>
@@ -11116,8 +12667,11 @@
       <c r="E517" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="518" spans="1:5">
+      <c r="F517" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6">
       <c r="A518" s="3" t="s">
         <v>162</v>
       </c>
@@ -11133,8 +12687,11 @@
       <c r="E518" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="519" spans="1:5">
+      <c r="F518" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6">
       <c r="A519" s="3" t="s">
         <v>163</v>
       </c>
@@ -11150,8 +12707,11 @@
       <c r="E519" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="520" spans="1:5">
+      <c r="F519" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6">
       <c r="A520" s="3" t="s">
         <v>164</v>
       </c>
@@ -11167,8 +12727,11 @@
       <c r="E520" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="521" spans="1:5">
+      <c r="F520" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6">
       <c r="A521" s="3" t="s">
         <v>522</v>
       </c>
@@ -11184,8 +12747,11 @@
       <c r="E521" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="522" spans="1:5">
+      <c r="F521" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="522" spans="1:6">
       <c r="A522" s="3" t="s">
         <v>523</v>
       </c>
@@ -11201,8 +12767,11 @@
       <c r="E522" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="523" spans="1:5">
+      <c r="F522" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="523" spans="1:6">
       <c r="A523" s="3" t="s">
         <v>524</v>
       </c>
@@ -11218,8 +12787,11 @@
       <c r="E523" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="524" spans="1:5">
+      <c r="F523" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="524" spans="1:6">
       <c r="A524" s="3" t="s">
         <v>525</v>
       </c>
@@ -11235,8 +12807,11 @@
       <c r="E524" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="525" spans="1:5">
+      <c r="F524" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="525" spans="1:6">
       <c r="A525" s="3" t="s">
         <v>526</v>
       </c>
@@ -11252,8 +12827,11 @@
       <c r="E525" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="526" spans="1:5">
+      <c r="F525" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="526" spans="1:6">
       <c r="A526" s="3" t="s">
         <v>527</v>
       </c>
@@ -11269,8 +12847,11 @@
       <c r="E526" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="527" spans="1:5">
+      <c r="F526" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="527" spans="1:6">
       <c r="A527" s="3" t="s">
         <v>528</v>
       </c>
@@ -11286,8 +12867,11 @@
       <c r="E527" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="528" spans="1:5">
+      <c r="F527" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="528" spans="1:6">
       <c r="A528" s="3" t="s">
         <v>529</v>
       </c>
@@ -11303,8 +12887,11 @@
       <c r="E528" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="529" spans="1:5">
+      <c r="F528" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="529" spans="1:6">
       <c r="A529" s="3" t="s">
         <v>530</v>
       </c>
@@ -11320,8 +12907,11 @@
       <c r="E529" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="530" spans="1:5">
+      <c r="F529" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="530" spans="1:6">
       <c r="A530" s="3" t="s">
         <v>531</v>
       </c>
@@ -11337,8 +12927,11 @@
       <c r="E530" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="531" spans="1:5">
+      <c r="F530" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="531" spans="1:6">
       <c r="A531" s="3" t="s">
         <v>532</v>
       </c>
@@ -11354,8 +12947,11 @@
       <c r="E531" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="532" spans="1:5">
+      <c r="F531" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="532" spans="1:6">
       <c r="A532" s="3" t="s">
         <v>221</v>
       </c>
@@ -11371,8 +12967,11 @@
       <c r="E532" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="533" spans="1:5">
+      <c r="F532" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="533" spans="1:6">
       <c r="A533" s="3" t="s">
         <v>222</v>
       </c>
@@ -11388,8 +12987,11 @@
       <c r="E533" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="534" spans="1:5">
+      <c r="F533" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="534" spans="1:6">
       <c r="A534" s="3" t="s">
         <v>223</v>
       </c>
@@ -11405,8 +13007,11 @@
       <c r="E534" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="535" spans="1:5">
+      <c r="F534" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="535" spans="1:6">
       <c r="A535" s="3" t="s">
         <v>224</v>
       </c>
@@ -11422,8 +13027,11 @@
       <c r="E535" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="536" spans="1:5">
+      <c r="F535" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="536" spans="1:6">
       <c r="A536" s="3" t="s">
         <v>225</v>
       </c>
@@ -11439,8 +13047,11 @@
       <c r="E536" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="537" spans="1:5">
+      <c r="F536" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="537" spans="1:6">
       <c r="A537" s="3" t="s">
         <v>226</v>
       </c>
@@ -11456,8 +13067,11 @@
       <c r="E537" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="538" spans="1:5">
+      <c r="F537" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="538" spans="1:6">
       <c r="A538" s="3" t="s">
         <v>227</v>
       </c>
@@ -11473,8 +13087,11 @@
       <c r="E538" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="539" spans="1:5">
+      <c r="F538" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="539" spans="1:6">
       <c r="A539" s="3" t="s">
         <v>228</v>
       </c>
@@ -11490,8 +13107,11 @@
       <c r="E539" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="540" spans="1:5">
+      <c r="F539" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="540" spans="1:6">
       <c r="A540" s="3" t="s">
         <v>229</v>
       </c>
@@ -11507,8 +13127,11 @@
       <c r="E540" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="541" spans="1:5">
+      <c r="F540" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="541" spans="1:6">
       <c r="A541" s="3" t="s">
         <v>230</v>
       </c>
@@ -11524,8 +13147,11 @@
       <c r="E541" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="542" spans="1:5">
+      <c r="F541" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="542" spans="1:6">
       <c r="A542" s="3" t="s">
         <v>231</v>
       </c>
@@ -11541,8 +13167,11 @@
       <c r="E542" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="543" spans="1:5">
+      <c r="F542" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="543" spans="1:6">
       <c r="A543" s="3" t="s">
         <v>232</v>
       </c>
@@ -11558,8 +13187,11 @@
       <c r="E543" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="544" spans="1:5">
+      <c r="F543" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="544" spans="1:6">
       <c r="A544" s="3" t="s">
         <v>233</v>
       </c>
@@ -11575,8 +13207,11 @@
       <c r="E544" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="545" spans="1:5">
+      <c r="F544" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="545" spans="1:6">
       <c r="A545" s="3" t="s">
         <v>234</v>
       </c>
@@ -11592,8 +13227,11 @@
       <c r="E545" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="546" spans="1:5">
+      <c r="F545" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="546" spans="1:6">
       <c r="A546" s="3" t="s">
         <v>235</v>
       </c>
@@ -11609,8 +13247,11 @@
       <c r="E546" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="547" spans="1:5">
+      <c r="F546" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="547" spans="1:6">
       <c r="A547" s="3" t="s">
         <v>236</v>
       </c>
@@ -11626,8 +13267,11 @@
       <c r="E547" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="548" spans="1:5">
+      <c r="F547" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="548" spans="1:6">
       <c r="A548" s="3" t="s">
         <v>237</v>
       </c>
@@ -11643,8 +13287,11 @@
       <c r="E548" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="549" spans="1:5">
+      <c r="F548" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="549" spans="1:6">
       <c r="A549" s="3" t="s">
         <v>238</v>
       </c>
@@ -11660,8 +13307,11 @@
       <c r="E549" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="550" spans="1:5">
+      <c r="F549" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="550" spans="1:6">
       <c r="A550" s="3" t="s">
         <v>239</v>
       </c>
@@ -11677,8 +13327,11 @@
       <c r="E550" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="551" spans="1:5">
+      <c r="F550" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="551" spans="1:6">
       <c r="A551" s="3" t="s">
         <v>240</v>
       </c>
@@ -11694,8 +13347,11 @@
       <c r="E551" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="552" spans="1:5">
+      <c r="F551" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="552" spans="1:6">
       <c r="A552" s="3" t="s">
         <v>584</v>
       </c>
@@ -11711,8 +13367,11 @@
       <c r="E552" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="553" spans="1:5">
+      <c r="F552" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="553" spans="1:6">
       <c r="A553" s="3" t="s">
         <v>585</v>
       </c>
@@ -11728,8 +13387,11 @@
       <c r="E553" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="554" spans="1:5">
+      <c r="F553" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="554" spans="1:6">
       <c r="A554" s="3" t="s">
         <v>361</v>
       </c>
@@ -11745,8 +13407,11 @@
       <c r="E554" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="555" spans="1:5">
+      <c r="F554" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="555" spans="1:6">
       <c r="A555" s="3" t="s">
         <v>578</v>
       </c>
@@ -11762,8 +13427,11 @@
       <c r="E555" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="556" spans="1:5">
+      <c r="F555" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="556" spans="1:6">
       <c r="A556" s="3" t="s">
         <v>97</v>
       </c>
@@ -11779,8 +13447,11 @@
       <c r="E556" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="557" spans="1:5">
+      <c r="F556" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="557" spans="1:6">
       <c r="A557" s="3" t="s">
         <v>505</v>
       </c>
@@ -11796,8 +13467,11 @@
       <c r="E557" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="558" spans="1:5">
+      <c r="F557" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="558" spans="1:6">
       <c r="A558" s="3" t="s">
         <v>586</v>
       </c>
@@ -11813,8 +13487,11 @@
       <c r="E558" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="559" spans="1:5">
+      <c r="F558" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="559" spans="1:6">
       <c r="A559" s="3" t="s">
         <v>458</v>
       </c>
@@ -11830,8 +13507,11 @@
       <c r="E559" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="560" spans="1:5">
+      <c r="F559" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="560" spans="1:6">
       <c r="A560" s="3" t="s">
         <v>587</v>
       </c>
@@ -11847,8 +13527,11 @@
       <c r="E560" s="4" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="561" spans="1:5">
+      <c r="F560" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="561" spans="1:6">
       <c r="A561" s="3" t="s">
         <v>332</v>
       </c>
@@ -11864,8 +13547,11 @@
       <c r="E561" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="562" spans="1:5">
+      <c r="F561" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="562" spans="1:6">
       <c r="A562" s="3" t="s">
         <v>588</v>
       </c>
@@ -11881,8 +13567,11 @@
       <c r="E562" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="563" spans="1:5">
+      <c r="F562" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="563" spans="1:6">
       <c r="A563" s="3" t="s">
         <v>589</v>
       </c>
@@ -11898,8 +13587,11 @@
       <c r="E563" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="564" spans="1:5">
+      <c r="F563" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="564" spans="1:6">
       <c r="A564" s="3" t="s">
         <v>590</v>
       </c>
@@ -11915,8 +13607,11 @@
       <c r="E564" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="565" spans="1:5">
+      <c r="F564" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="565" spans="1:6">
       <c r="A565" s="3" t="s">
         <v>141</v>
       </c>
@@ -11932,8 +13627,11 @@
       <c r="E565" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="566" spans="1:5">
+      <c r="F565" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="566" spans="1:6">
       <c r="A566" s="3" t="s">
         <v>591</v>
       </c>
@@ -11949,8 +13647,11 @@
       <c r="E566" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="567" spans="1:5">
+      <c r="F566" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="567" spans="1:6">
       <c r="A567" s="3" t="s">
         <v>408</v>
       </c>
@@ -11966,8 +13667,11 @@
       <c r="E567" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="568" spans="1:5">
+      <c r="F567" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="568" spans="1:6">
       <c r="A568" s="3" t="s">
         <v>546</v>
       </c>
@@ -11983,8 +13687,11 @@
       <c r="E568" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="569" spans="1:5">
+      <c r="F568" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="569" spans="1:6">
       <c r="A569" s="3" t="s">
         <v>545</v>
       </c>
@@ -12000,8 +13707,11 @@
       <c r="E569" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="570" spans="1:5">
+      <c r="F569" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="570" spans="1:6">
       <c r="A570" s="3" t="s">
         <v>519</v>
       </c>
@@ -12017,8 +13727,11 @@
       <c r="E570" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="571" spans="1:5">
+      <c r="F570" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="571" spans="1:6">
       <c r="A571" s="3" t="s">
         <v>431</v>
       </c>
@@ -12034,8 +13747,11 @@
       <c r="E571" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="572" spans="1:5">
+      <c r="F571" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="572" spans="1:6">
       <c r="A572" s="3" t="s">
         <v>592</v>
       </c>
@@ -12051,8 +13767,11 @@
       <c r="E572" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="573" spans="1:5">
+      <c r="F572" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="573" spans="1:6">
       <c r="A573" s="3" t="s">
         <v>593</v>
       </c>
@@ -12068,8 +13787,11 @@
       <c r="E573" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="574" spans="1:5">
+      <c r="F573" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="574" spans="1:6">
       <c r="A574" s="3" t="s">
         <v>551</v>
       </c>
@@ -12085,8 +13807,11 @@
       <c r="E574" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="575" spans="1:5">
+      <c r="F574" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="575" spans="1:6">
       <c r="A575" s="3" t="s">
         <v>594</v>
       </c>
@@ -12102,8 +13827,11 @@
       <c r="E575" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="576" spans="1:5">
+      <c r="F575" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="576" spans="1:6">
       <c r="A576" s="3" t="s">
         <v>595</v>
       </c>
@@ -12119,8 +13847,11 @@
       <c r="E576" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="577" spans="1:5">
+      <c r="F576" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="577" spans="1:6">
       <c r="A577" s="3" t="s">
         <v>106</v>
       </c>
@@ -12136,8 +13867,11 @@
       <c r="E577" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="578" spans="1:5">
+      <c r="F577" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="578" spans="1:6">
       <c r="A578" s="3" t="s">
         <v>36</v>
       </c>
@@ -12153,8 +13887,11 @@
       <c r="E578" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="579" spans="1:5">
+      <c r="F578" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="579" spans="1:6">
       <c r="A579" s="3" t="s">
         <v>373</v>
       </c>
@@ -12170,8 +13907,11 @@
       <c r="E579" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="580" spans="1:5">
+      <c r="F579" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="580" spans="1:6">
       <c r="A580" s="3" t="s">
         <v>596</v>
       </c>
@@ -12187,8 +13927,11 @@
       <c r="E580" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="581" spans="1:5">
+      <c r="F580" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="581" spans="1:6">
       <c r="A581" s="3" t="s">
         <v>518</v>
       </c>
@@ -12204,8 +13947,11 @@
       <c r="E581" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="582" spans="1:5">
+      <c r="F581" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="582" spans="1:6">
       <c r="A582" s="3" t="s">
         <v>563</v>
       </c>
@@ -12221,8 +13967,11 @@
       <c r="E582" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="583" spans="1:5">
+      <c r="F582" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="583" spans="1:6">
       <c r="A583" s="3" t="s">
         <v>105</v>
       </c>
@@ -12238,8 +13987,11 @@
       <c r="E583" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="584" spans="1:5">
+      <c r="F583" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="584" spans="1:6">
       <c r="A584" s="3" t="s">
         <v>559</v>
       </c>
@@ -12255,8 +14007,11 @@
       <c r="E584" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="585" spans="1:5">
+      <c r="F584" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="585" spans="1:6">
       <c r="A585" s="3" t="s">
         <v>402</v>
       </c>
@@ -12272,8 +14027,11 @@
       <c r="E585" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="586" spans="1:5">
+      <c r="F585" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="586" spans="1:6">
       <c r="A586" s="3" t="s">
         <v>459</v>
       </c>
@@ -12289,8 +14047,11 @@
       <c r="E586" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="587" spans="1:5">
+      <c r="F586" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="587" spans="1:6">
       <c r="A587" s="3" t="s">
         <v>598</v>
       </c>
@@ -12306,8 +14067,11 @@
       <c r="E587" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="588" spans="1:5">
+      <c r="F587" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="588" spans="1:6">
       <c r="A588" s="3" t="s">
         <v>599</v>
       </c>
@@ -12323,8 +14087,11 @@
       <c r="E588" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="589" spans="1:5">
+      <c r="F588" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="589" spans="1:6">
       <c r="A589" s="3" t="s">
         <v>600</v>
       </c>
@@ -12340,8 +14107,11 @@
       <c r="E589" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="590" spans="1:5">
+      <c r="F589" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="590" spans="1:6">
       <c r="A590" s="3" t="s">
         <v>515</v>
       </c>
@@ -12357,8 +14127,11 @@
       <c r="E590" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="591" spans="1:5">
+      <c r="F590" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="591" spans="1:6">
       <c r="A591" s="3" t="s">
         <v>471</v>
       </c>
@@ -12374,8 +14147,11 @@
       <c r="E591" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="592" spans="1:5">
+      <c r="F591" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="592" spans="1:6">
       <c r="A592" s="3" t="s">
         <v>583</v>
       </c>
@@ -12391,8 +14167,11 @@
       <c r="E592" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="593" spans="1:5">
+      <c r="F592" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="593" spans="1:6">
       <c r="A593" s="3" t="s">
         <v>147</v>
       </c>
@@ -12408,8 +14187,11 @@
       <c r="E593" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="594" spans="1:5">
+      <c r="F593" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="594" spans="1:6">
       <c r="A594" s="3" t="s">
         <v>560</v>
       </c>
@@ -12425,8 +14207,11 @@
       <c r="E594" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="595" spans="1:5">
+      <c r="F594" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="595" spans="1:6">
       <c r="A595" s="3" t="s">
         <v>310</v>
       </c>
@@ -12442,8 +14227,11 @@
       <c r="E595" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="596" spans="1:5">
+      <c r="F595" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="596" spans="1:6">
       <c r="A596" s="3" t="s">
         <v>437</v>
       </c>
@@ -12459,8 +14247,11 @@
       <c r="E596" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="597" spans="1:5">
+      <c r="F596" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="597" spans="1:6">
       <c r="A597" s="3" t="s">
         <v>371</v>
       </c>
@@ -12476,8 +14267,11 @@
       <c r="E597" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="598" spans="1:5">
+      <c r="F597" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="598" spans="1:6">
       <c r="A598" s="3" t="s">
         <v>457</v>
       </c>
@@ -12493,8 +14287,11 @@
       <c r="E598" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="599" spans="1:5">
+      <c r="F598" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="599" spans="1:6">
       <c r="A599" s="3" t="s">
         <v>363</v>
       </c>
@@ -12510,8 +14307,11 @@
       <c r="E599" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="600" spans="1:5">
+      <c r="F599" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="600" spans="1:6">
       <c r="A600" s="3" t="s">
         <v>364</v>
       </c>
@@ -12527,8 +14327,11 @@
       <c r="E600" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="601" spans="1:5">
+      <c r="F600" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="601" spans="1:6">
       <c r="A601" s="3" t="s">
         <v>2</v>
       </c>
@@ -12544,8 +14347,11 @@
       <c r="E601" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="602" spans="1:5">
+      <c r="F601" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="602" spans="1:6">
       <c r="A602" s="3" t="s">
         <v>404</v>
       </c>
@@ -12561,8 +14367,11 @@
       <c r="E602" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="603" spans="1:5">
+      <c r="F602" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="603" spans="1:6">
       <c r="A603" s="3" t="s">
         <v>601</v>
       </c>
@@ -12578,8 +14387,11 @@
       <c r="E603" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="604" spans="1:5">
+      <c r="F603" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="604" spans="1:6">
       <c r="A604" s="3" t="s">
         <v>602</v>
       </c>
@@ -12595,8 +14407,11 @@
       <c r="E604" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="605" spans="1:5">
+      <c r="F604" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="605" spans="1:6">
       <c r="A605" s="3" t="s">
         <v>603</v>
       </c>
@@ -12612,8 +14427,11 @@
       <c r="E605" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="606" spans="1:5">
+      <c r="F605" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="606" spans="1:6">
       <c r="A606" s="3" t="s">
         <v>414</v>
       </c>
@@ -12629,8 +14447,11 @@
       <c r="E606" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="607" spans="1:5">
+      <c r="F606" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="607" spans="1:6">
       <c r="A607" s="3" t="s">
         <v>415</v>
       </c>
@@ -12646,8 +14467,11 @@
       <c r="E607" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="608" spans="1:5">
+      <c r="F607" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="608" spans="1:6">
       <c r="A608" s="3" t="s">
         <v>416</v>
       </c>
@@ -12663,8 +14487,11 @@
       <c r="E608" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="609" spans="1:5">
+      <c r="F608" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="609" spans="1:6">
       <c r="A609" s="3" t="s">
         <v>564</v>
       </c>
@@ -12680,8 +14507,11 @@
       <c r="E609" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="610" spans="1:5">
+      <c r="F609" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="610" spans="1:6">
       <c r="A610" s="3" t="s">
         <v>575</v>
       </c>
@@ -12697,8 +14527,11 @@
       <c r="E610" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="611" spans="1:5">
+      <c r="F610" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="611" spans="1:6">
       <c r="A611" s="3" t="s">
         <v>311</v>
       </c>
@@ -12714,8 +14547,11 @@
       <c r="E611" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="612" spans="1:5">
+      <c r="F611" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="612" spans="1:6">
       <c r="A612" s="3" t="s">
         <v>513</v>
       </c>
@@ -12731,8 +14567,11 @@
       <c r="E612" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="613" spans="1:5">
+      <c r="F612" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="613" spans="1:6">
       <c r="A613" s="3" t="s">
         <v>604</v>
       </c>
@@ -12748,8 +14587,11 @@
       <c r="E613" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="614" spans="1:5">
+      <c r="F613" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="614" spans="1:6">
       <c r="A614" s="3" t="s">
         <v>605</v>
       </c>
@@ -12765,8 +14607,11 @@
       <c r="E614" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="615" spans="1:5">
+      <c r="F614" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="615" spans="1:6">
       <c r="A615" s="3" t="s">
         <v>606</v>
       </c>
@@ -12782,8 +14627,11 @@
       <c r="E615" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="616" spans="1:5">
+      <c r="F615" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="616" spans="1:6">
       <c r="A616" s="3" t="s">
         <v>300</v>
       </c>
@@ -12799,8 +14647,11 @@
       <c r="E616" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="617" spans="1:5">
+      <c r="F616" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="617" spans="1:6">
       <c r="A617" s="3" t="s">
         <v>597</v>
       </c>
@@ -12816,8 +14667,11 @@
       <c r="E617" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="618" spans="1:5">
+      <c r="F617" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="618" spans="1:6">
       <c r="A618" s="3" t="s">
         <v>411</v>
       </c>
@@ -12833,8 +14687,11 @@
       <c r="E618" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="619" spans="1:5">
+      <c r="F618" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="619" spans="1:6">
       <c r="A619" s="3" t="s">
         <v>23</v>
       </c>
@@ -12850,8 +14707,11 @@
       <c r="E619" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="620" spans="1:5">
+      <c r="F619" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="620" spans="1:6">
       <c r="A620" s="3" t="s">
         <v>542</v>
       </c>
@@ -12867,8 +14727,11 @@
       <c r="E620" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="621" spans="1:5">
+      <c r="F620" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="621" spans="1:6">
       <c r="A621" s="3" t="s">
         <v>398</v>
       </c>
@@ -12884,8 +14747,11 @@
       <c r="E621" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="622" spans="1:5">
+      <c r="F621" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="622" spans="1:6">
       <c r="A622" s="3" t="s">
         <v>392</v>
       </c>
@@ -12901,8 +14767,11 @@
       <c r="E622" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="623" spans="1:5">
+      <c r="F622" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="623" spans="1:6">
       <c r="A623" s="3" t="s">
         <v>395</v>
       </c>
@@ -12918,8 +14787,11 @@
       <c r="E623" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="624" spans="1:5">
+      <c r="F623" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="624" spans="1:6">
       <c r="A624" s="3" t="s">
         <v>594</v>
       </c>
@@ -12935,8 +14807,11 @@
       <c r="E624" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="625" spans="1:5">
+      <c r="F624" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="625" spans="1:6">
       <c r="A625" s="3" t="s">
         <v>412</v>
       </c>
@@ -12952,8 +14827,11 @@
       <c r="E625" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="626" spans="1:5">
+      <c r="F625" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="626" spans="1:6">
       <c r="A626" s="3" t="s">
         <v>255</v>
       </c>
@@ -12969,8 +14847,11 @@
       <c r="E626" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="627" spans="1:5">
+      <c r="F626" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="627" spans="1:6">
       <c r="A627" s="3" t="s">
         <v>454</v>
       </c>
@@ -12986,8 +14867,11 @@
       <c r="E627" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="628" spans="1:5">
+      <c r="F627" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="628" spans="1:6">
       <c r="A628" s="3" t="s">
         <v>265</v>
       </c>
@@ -13003,8 +14887,11 @@
       <c r="E628" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="629" spans="1:5">
+      <c r="F628" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="629" spans="1:6">
       <c r="A629" s="3" t="s">
         <v>417</v>
       </c>
@@ -13020,8 +14907,11 @@
       <c r="E629" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="630" spans="1:5">
+      <c r="F629" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="630" spans="1:6">
       <c r="A630" s="3" t="s">
         <v>419</v>
       </c>
@@ -13037,8 +14927,11 @@
       <c r="E630" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="631" spans="1:5">
+      <c r="F630" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="631" spans="1:6">
       <c r="A631" s="3" t="s">
         <v>544</v>
       </c>
@@ -13054,8 +14947,11 @@
       <c r="E631" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="632" spans="1:5">
+      <c r="F631" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="632" spans="1:6">
       <c r="A632" s="3" t="s">
         <v>453</v>
       </c>
@@ -13071,8 +14967,11 @@
       <c r="E632" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="633" spans="1:5">
+      <c r="F632" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="633" spans="1:6">
       <c r="A633" s="3" t="s">
         <v>454</v>
       </c>
@@ -13088,8 +14987,11 @@
       <c r="E633" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="634" spans="1:5">
+      <c r="F633" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="634" spans="1:6">
       <c r="A634" s="3" t="s">
         <v>256</v>
       </c>
@@ -13105,8 +15007,11 @@
       <c r="E634" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="635" spans="1:5">
+      <c r="F634" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="635" spans="1:6">
       <c r="A635" s="3" t="s">
         <v>392</v>
       </c>
@@ -13122,8 +15027,11 @@
       <c r="E635" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="636" spans="1:5">
+      <c r="F635" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="636" spans="1:6">
       <c r="A636" s="3" t="s">
         <v>332</v>
       </c>
@@ -13139,8 +15047,11 @@
       <c r="E636" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="637" spans="1:5">
+      <c r="F636" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="637" spans="1:6">
       <c r="A637" s="3" t="s">
         <v>16</v>
       </c>
@@ -13156,8 +15067,11 @@
       <c r="E637" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="638" spans="1:5">
+      <c r="F637" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="638" spans="1:6">
       <c r="A638" s="3" t="s">
         <v>17</v>
       </c>
@@ -13173,8 +15087,11 @@
       <c r="E638" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="639" spans="1:5">
+      <c r="F638" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="639" spans="1:6">
       <c r="A639" s="3" t="s">
         <v>401</v>
       </c>
@@ -13190,8 +15107,11 @@
       <c r="E639" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="640" spans="1:5">
+      <c r="F639" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="640" spans="1:6">
       <c r="A640" s="3" t="s">
         <v>607</v>
       </c>
@@ -13207,8 +15127,11 @@
       <c r="E640" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="641" spans="1:5">
+      <c r="F640" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="641" spans="1:6">
       <c r="A641" s="3" t="s">
         <v>170</v>
       </c>
@@ -13224,8 +15147,11 @@
       <c r="E641" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="642" spans="1:5">
+      <c r="F641" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="642" spans="1:6">
       <c r="A642" s="3" t="s">
         <v>16</v>
       </c>
@@ -13241,8 +15167,11 @@
       <c r="E642" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="643" spans="1:5">
+      <c r="F642" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="643" spans="1:6">
       <c r="A643" s="3" t="s">
         <v>594</v>
       </c>
@@ -13258,8 +15187,11 @@
       <c r="E643" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="644" spans="1:5">
+      <c r="F643" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="644" spans="1:6">
       <c r="A644" s="3" t="s">
         <v>41</v>
       </c>
@@ -13275,8 +15207,11 @@
       <c r="E644" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="645" spans="1:5">
+      <c r="F644" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="645" spans="1:6">
       <c r="A645" s="3" t="s">
         <v>133</v>
       </c>
@@ -13292,8 +15227,11 @@
       <c r="E645" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="646" spans="1:5">
+      <c r="F645" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="646" spans="1:6">
       <c r="A646" s="3" t="s">
         <v>72</v>
       </c>
@@ -13309,8 +15247,11 @@
       <c r="E646" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="647" spans="1:5">
+      <c r="F646" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="647" spans="1:6">
       <c r="A647" s="3" t="s">
         <v>510</v>
       </c>
@@ -13326,8 +15267,11 @@
       <c r="E647" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="648" spans="1:5">
+      <c r="F647" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="648" spans="1:6">
       <c r="A648" s="3" t="s">
         <v>608</v>
       </c>
@@ -13343,57 +15287,60 @@
       <c r="E648" s="4" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="649" spans="1:5">
+      <c r="F648" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="649" spans="1:6">
       <c r="A649" s="3"/>
       <c r="B649" s="5"/>
       <c r="C649" s="7"/>
       <c r="D649" s="7"/>
       <c r="E649" s="4"/>
     </row>
-    <row r="650" spans="1:5">
+    <row r="650" spans="1:6">
       <c r="A650" s="3"/>
       <c r="B650" s="5"/>
       <c r="C650" s="7"/>
       <c r="D650" s="7"/>
       <c r="E650" s="4"/>
     </row>
-    <row r="651" spans="1:5">
+    <row r="651" spans="1:6">
       <c r="A651" s="3"/>
       <c r="B651" s="5"/>
       <c r="C651" s="7"/>
       <c r="D651" s="7"/>
       <c r="E651" s="4"/>
     </row>
-    <row r="652" spans="1:5">
+    <row r="652" spans="1:6">
       <c r="A652" s="3"/>
       <c r="B652" s="5"/>
       <c r="C652" s="7"/>
       <c r="D652" s="7"/>
       <c r="E652" s="4"/>
     </row>
-    <row r="653" spans="1:5">
+    <row r="653" spans="1:6">
       <c r="A653" s="3"/>
       <c r="B653" s="5"/>
       <c r="C653" s="7"/>
       <c r="D653" s="7"/>
       <c r="E653" s="4"/>
     </row>
-    <row r="654" spans="1:5">
+    <row r="654" spans="1:6">
       <c r="A654" s="3"/>
       <c r="B654" s="5"/>
       <c r="C654" s="7"/>
       <c r="D654" s="7"/>
       <c r="E654" s="4"/>
     </row>
-    <row r="655" spans="1:5">
+    <row r="655" spans="1:6">
       <c r="A655" s="3"/>
       <c r="B655" s="5"/>
       <c r="C655" s="7"/>
       <c r="D655" s="7"/>
       <c r="E655" s="4"/>
     </row>
-    <row r="656" spans="1:5">
+    <row r="656" spans="1:6">
       <c r="A656" s="3"/>
       <c r="B656" s="5"/>
       <c r="C656" s="7"/>
@@ -70312,15 +72259,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <TaxCatchAll xmlns="477cc4b0-0066-4088-82a8-f8e908d5e20c" xsi:nil="true"/>
@@ -70329,6 +72267,15 @@
     </lcf76f155ced4ddcb4097134ff3c332f>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -70351,14 +72298,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12324D94-7B24-480D-9398-F1BCD8252322}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3425C370-B5F7-4368-9643-2B9A649E16D9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -70369,6 +72308,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12324D94-7B24-480D-9398-F1BCD8252322}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{202412c0-1e7d-4ccc-99a7-7c8f0a21f86d}" enabled="1" method="Standard" siteId="{0d993ad3-fa73-421a-b129-1fe5590103f3}" contentBits="1" removed="0"/>

--- a/database/POs Pendentes.xlsx
+++ b/database/POs Pendentes.xlsx
@@ -58,157 +58,157 @@
     <t>company_id</t>
   </si>
   <si>
-    <t>AA00002281867</t>
-  </si>
-  <si>
-    <t>AA00002281897</t>
-  </si>
-  <si>
-    <t>AA00002281893</t>
-  </si>
-  <si>
-    <t>AA00002274288</t>
-  </si>
-  <si>
-    <t>AA00002274285</t>
-  </si>
-  <si>
-    <t>AA00002253562</t>
-  </si>
-  <si>
-    <t>AA00002284877</t>
-  </si>
-  <si>
-    <t>AA00002280721</t>
-  </si>
-  <si>
-    <t>DTR0000471764</t>
-  </si>
-  <si>
-    <t>LM00000277634</t>
-  </si>
-  <si>
-    <t>LM00000277629</t>
-  </si>
-  <si>
-    <t>LM00000276860</t>
-  </si>
-  <si>
-    <t>DTR0000257232</t>
-  </si>
-  <si>
-    <t>AA00002274291</t>
-  </si>
-  <si>
-    <t>AA00002281866</t>
-  </si>
-  <si>
-    <t>AA00002253582</t>
-  </si>
-  <si>
-    <t>AA00002253588</t>
-  </si>
-  <si>
-    <t>AA00002253586</t>
-  </si>
-  <si>
-    <t>AA00002253583</t>
-  </si>
-  <si>
-    <t>AA00002310617</t>
-  </si>
-  <si>
-    <t>NH00001787308</t>
-  </si>
-  <si>
-    <t>CD00001864805</t>
-  </si>
-  <si>
-    <t>DTR0009907822</t>
-  </si>
-  <si>
-    <t>DTR0009907737</t>
-  </si>
-  <si>
-    <t>DTR0009907273</t>
-  </si>
-  <si>
-    <t>AA00002274236</t>
-  </si>
-  <si>
-    <t>AA00002274213</t>
-  </si>
-  <si>
-    <t>AA00002274210</t>
-  </si>
-  <si>
-    <t>AA00002273915</t>
-  </si>
-  <si>
-    <t>AA00002252534</t>
-  </si>
-  <si>
-    <t>AA00002252478</t>
-  </si>
-  <si>
-    <t>AA00002252479</t>
-  </si>
-  <si>
-    <t>DTR0000015396</t>
-  </si>
-  <si>
-    <t>AA00002252468</t>
-  </si>
-  <si>
-    <t>AA00002252469</t>
-  </si>
-  <si>
-    <t>AA00002294765</t>
-  </si>
-  <si>
-    <t>AA00002294801</t>
-  </si>
-  <si>
-    <t>AA00002294675</t>
-  </si>
-  <si>
-    <t>DTR0000388840</t>
-  </si>
-  <si>
-    <t>AA00002290885</t>
-  </si>
-  <si>
-    <t>AA00002345920</t>
-  </si>
-  <si>
-    <t>AA00002345921</t>
-  </si>
-  <si>
-    <t>DTR0009907851</t>
-  </si>
-  <si>
-    <t>DTR0009907842</t>
-  </si>
-  <si>
-    <t>DTR0009907841</t>
-  </si>
-  <si>
-    <t>DTR0009907741</t>
-  </si>
-  <si>
-    <t>DTR0009907740</t>
-  </si>
-  <si>
-    <t>DTR0009907739</t>
-  </si>
-  <si>
     <t>PC</t>
   </si>
   <si>
     <t>M</t>
   </si>
   <si>
-    <t>AA00002273914</t>
+    <t>2273914</t>
+  </si>
+  <si>
+    <t>2281867</t>
+  </si>
+  <si>
+    <t>2281897</t>
+  </si>
+  <si>
+    <t>2281893</t>
+  </si>
+  <si>
+    <t>2274288</t>
+  </si>
+  <si>
+    <t>2274285</t>
+  </si>
+  <si>
+    <t>2253562</t>
+  </si>
+  <si>
+    <t>2284877</t>
+  </si>
+  <si>
+    <t>2280721</t>
+  </si>
+  <si>
+    <t>0471764</t>
+  </si>
+  <si>
+    <t>0277634</t>
+  </si>
+  <si>
+    <t>0277629</t>
+  </si>
+  <si>
+    <t>0276860</t>
+  </si>
+  <si>
+    <t>0257232</t>
+  </si>
+  <si>
+    <t>2274291</t>
+  </si>
+  <si>
+    <t>2281866</t>
+  </si>
+  <si>
+    <t>2253582</t>
+  </si>
+  <si>
+    <t>2253588</t>
+  </si>
+  <si>
+    <t>2253586</t>
+  </si>
+  <si>
+    <t>2253583</t>
+  </si>
+  <si>
+    <t>2310617</t>
+  </si>
+  <si>
+    <t>1787308</t>
+  </si>
+  <si>
+    <t>1864805</t>
+  </si>
+  <si>
+    <t>9907822</t>
+  </si>
+  <si>
+    <t>9907737</t>
+  </si>
+  <si>
+    <t>9907273</t>
+  </si>
+  <si>
+    <t>2274236</t>
+  </si>
+  <si>
+    <t>2274213</t>
+  </si>
+  <si>
+    <t>2274210</t>
+  </si>
+  <si>
+    <t>2273915</t>
+  </si>
+  <si>
+    <t>2252534</t>
+  </si>
+  <si>
+    <t>2252478</t>
+  </si>
+  <si>
+    <t>2252479</t>
+  </si>
+  <si>
+    <t>0015396</t>
+  </si>
+  <si>
+    <t>2252468</t>
+  </si>
+  <si>
+    <t>2252469</t>
+  </si>
+  <si>
+    <t>2294765</t>
+  </si>
+  <si>
+    <t>2294801</t>
+  </si>
+  <si>
+    <t>2294675</t>
+  </si>
+  <si>
+    <t>0388840</t>
+  </si>
+  <si>
+    <t>2290885</t>
+  </si>
+  <si>
+    <t>2345920</t>
+  </si>
+  <si>
+    <t>2345921</t>
+  </si>
+  <si>
+    <t>9907851</t>
+  </si>
+  <si>
+    <t>9907842</t>
+  </si>
+  <si>
+    <t>9907841</t>
+  </si>
+  <si>
+    <t>9907741</t>
+  </si>
+  <si>
+    <t>9907740</t>
+  </si>
+  <si>
+    <t>9907739</t>
   </si>
 </sst>
 </file>
@@ -679,7 +679,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>56</v>
+        <v>8</v>
       </c>
       <c r="B2" s="5">
         <v>3696</v>
@@ -691,7 +691,7 @@
         <v>76681</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F2" s="7">
         <v>5</v>
@@ -699,7 +699,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B3" s="5">
         <v>5760</v>
@@ -711,7 +711,7 @@
         <v>25566</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F3" s="7">
         <v>5</v>
@@ -719,7 +719,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" s="5">
         <v>750.48</v>
@@ -731,7 +731,7 @@
         <v>50490</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F4" s="7">
         <v>5</v>
@@ -739,7 +739,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B5" s="5">
         <v>2196</v>
@@ -751,7 +751,7 @@
         <v>32234</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F5" s="7">
         <v>5</v>
@@ -759,7 +759,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B6" s="5">
         <v>410.4</v>
@@ -771,7 +771,7 @@
         <v>73239</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F6" s="7">
         <v>5</v>
@@ -779,7 +779,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" s="5">
         <v>172.79999999999998</v>
@@ -791,7 +791,7 @@
         <v>95423</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F7" s="7">
         <v>5</v>
@@ -799,7 +799,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B8" s="5">
         <v>828</v>
@@ -811,7 +811,7 @@
         <v>73551</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F8" s="7">
         <v>5</v>
@@ -819,7 +819,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B9" s="5">
         <v>48</v>
@@ -831,7 +831,7 @@
         <v>29812</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F9" s="7">
         <v>5</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B10" s="5">
         <v>48</v>
@@ -851,7 +851,7 @@
         <v>74539</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F10" s="7">
         <v>5</v>
@@ -859,7 +859,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B11" s="5">
         <v>528</v>
@@ -871,7 +871,7 @@
         <v>79693</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F11" s="7">
         <v>5</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B12" s="5">
         <v>93.6</v>
@@ -891,7 +891,7 @@
         <v>76504</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F12" s="7">
         <v>5</v>
@@ -899,7 +899,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B13" s="5">
         <v>1145193.6000000001</v>
@@ -911,7 +911,7 @@
         <v>35728</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F13" s="7">
         <v>5</v>
@@ -919,7 +919,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B14" s="5">
         <v>242472.72000000003</v>
@@ -931,7 +931,7 @@
         <v>70252</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F14" s="7">
         <v>5</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B15" s="5">
         <v>900</v>
@@ -951,7 +951,7 @@
         <v>80502</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F15" s="7">
         <v>5</v>
@@ -959,7 +959,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="B16" s="5">
         <v>320796.24</v>
@@ -971,7 +971,7 @@
         <v>49055</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F16" s="7">
         <v>5</v>
@@ -979,7 +979,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B17" s="5">
         <v>293100.96000000002</v>
@@ -991,7 +991,7 @@
         <v>42562</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F17" s="7">
         <v>5</v>
@@ -999,7 +999,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B18" s="5">
         <v>303946.56</v>
@@ -1011,7 +1011,7 @@
         <v>69860</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F18" s="7">
         <v>5</v>
@@ -1019,7 +1019,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B19" s="5">
         <v>24552</v>
@@ -1031,7 +1031,7 @@
         <v>45343</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F19" s="7">
         <v>5</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B20" s="5">
         <v>24552</v>
@@ -1051,7 +1051,7 @@
         <v>85888</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F20" s="7">
         <v>5</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B21" s="5">
         <v>14354.400000000001</v>
@@ -1071,7 +1071,7 @@
         <v>39576</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F21" s="7">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B22" s="5">
         <v>13637.28</v>
@@ -1091,7 +1091,7 @@
         <v>79080</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F22" s="7">
         <v>5</v>
@@ -1099,7 +1099,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="B23" s="5">
         <v>13637.28</v>
@@ -1111,7 +1111,7 @@
         <v>57864</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F23" s="7">
         <v>5</v>
@@ -1119,7 +1119,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="B24" s="5">
         <v>13637.28</v>
@@ -1131,7 +1131,7 @@
         <v>26966</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F24" s="7">
         <v>5</v>
@@ -1139,7 +1139,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="B25" s="5">
         <v>29348.639999999999</v>
@@ -1151,7 +1151,7 @@
         <v>79350</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F25" s="7">
         <v>5</v>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B26" s="5">
         <v>3438.24</v>
@@ -1171,7 +1171,7 @@
         <v>87184</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F26" s="7">
         <v>5</v>
@@ -1179,7 +1179,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B27" s="5">
         <v>2910.7200000000003</v>
@@ -1191,7 +1191,7 @@
         <v>51392</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F27" s="7">
         <v>5</v>
@@ -1199,7 +1199,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B28" s="5">
         <v>15320.64</v>
@@ -1211,7 +1211,7 @@
         <v>30151</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F28" s="7">
         <v>5</v>
@@ -1219,7 +1219,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B29" s="5">
         <v>3875.04</v>
@@ -1231,7 +1231,7 @@
         <v>93825</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F29" s="7">
         <v>5</v>
@@ -1239,7 +1239,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B30" s="5">
         <v>3282.7200000000003</v>
@@ -1251,7 +1251,7 @@
         <v>11688</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F30" s="7">
         <v>5</v>
@@ -1259,7 +1259,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5">
         <v>3163.32</v>
@@ -1271,7 +1271,7 @@
         <v>54537</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F31" s="7">
         <v>5</v>
@@ -1279,7 +1279,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5">
         <v>937986.11999999988</v>
@@ -1291,7 +1291,7 @@
         <v>51932</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F32" s="7">
         <v>5</v>
@@ -1299,7 +1299,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5">
         <v>24680.159999999996</v>
@@ -1311,7 +1311,7 @@
         <v>15751</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F33" s="7">
         <v>5</v>
@@ -1319,7 +1319,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5">
         <v>31309.919999999998</v>
@@ -1331,7 +1331,7 @@
         <v>83207</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F34" s="7">
         <v>5</v>
@@ -1339,7 +1339,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B35" s="5">
         <v>31309.919999999998</v>
@@ -1351,7 +1351,7 @@
         <v>93653</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F35" s="7">
         <v>5</v>
@@ -1359,7 +1359,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B36" s="5">
         <v>31309.919999999998</v>
@@ -1371,7 +1371,7 @@
         <v>62497</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F36" s="7">
         <v>5</v>
@@ -1379,7 +1379,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B37" s="5">
         <v>31309.919999999998</v>
@@ -1391,7 +1391,7 @@
         <v>35421</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F37" s="7">
         <v>5</v>
@@ -1399,7 +1399,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B38" s="5">
         <v>31309.919999999998</v>
@@ -1411,7 +1411,7 @@
         <v>98215</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F38" s="7">
         <v>5</v>
@@ -1419,7 +1419,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B39" s="5">
         <v>31309.919999999998</v>
@@ -1431,7 +1431,7 @@
         <v>83026</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>55</v>
+        <v>7</v>
       </c>
       <c r="F39" s="7">
         <v>5</v>
@@ -1439,7 +1439,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B40" s="5">
         <v>775.02</v>
@@ -1451,7 +1451,7 @@
         <v>74107</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F40" s="7">
         <v>5</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B41" s="5">
         <v>2704.36</v>
@@ -1471,7 +1471,7 @@
         <v>14996</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F41" s="7">
         <v>5</v>
@@ -1479,7 +1479,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B42" s="5">
         <v>482.46</v>
@@ -1491,7 +1491,7 @@
         <v>31880</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F42" s="7">
         <v>5</v>
@@ -1499,7 +1499,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B43" s="5">
         <v>97736.24</v>
@@ -1511,7 +1511,7 @@
         <v>20052</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F43" s="7">
         <v>5</v>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B44" s="5">
         <v>14853.649999999998</v>
@@ -1531,7 +1531,7 @@
         <v>70471</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F44" s="7">
         <v>5</v>
@@ -1539,7 +1539,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B45" s="5">
         <v>995.46</v>
@@ -1551,7 +1551,7 @@
         <v>64837</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F45" s="7">
         <v>5</v>
@@ -1559,7 +1559,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B46" s="5">
         <v>3055.3500000000004</v>
@@ -1571,7 +1571,7 @@
         <v>35649</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F46" s="7">
         <v>5</v>
@@ -1579,7 +1579,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B47" s="5">
         <v>18835.759999999998</v>
@@ -1591,7 +1591,7 @@
         <v>70080</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F47" s="7">
         <v>5</v>
@@ -1599,7 +1599,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B48" s="5">
         <v>53649.279999999999</v>
@@ -1611,7 +1611,7 @@
         <v>78438</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F48" s="7">
         <v>5</v>
@@ -1619,7 +1619,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B49" s="5">
         <v>40396.199999999997</v>
@@ -1631,7 +1631,7 @@
         <v>34543</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F49" s="7">
         <v>5</v>
@@ -1639,7 +1639,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B50" s="5">
         <v>8594.56</v>
@@ -1651,7 +1651,7 @@
         <v>56186</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>54</v>
+        <v>6</v>
       </c>
       <c r="F50" s="7">
         <v>5</v>
@@ -58405,17 +58405,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="477cc4b0-0066-4088-82a8-f8e908d5e20c" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a2028d18-6aea-4b98-9583-fc23b0b95105">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EFAEB830C5C72940960B68A8710E45EA" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="88e9a867459e469803d2f07c8ed2f3f8">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a2028d18-6aea-4b98-9583-fc23b0b95105" xmlns:ns3="477cc4b0-0066-4088-82a8-f8e908d5e20c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9060328819ca9b7b18404ffe09a89c4a" ns2:_="" ns3:_="">
     <xsd:import namespace="a2028d18-6aea-4b98-9583-fc23b0b95105"/>
@@ -58644,6 +58633,17 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="477cc4b0-0066-4088-82a8-f8e908d5e20c" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a2028d18-6aea-4b98-9583-fc23b0b95105">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{12324D94-7B24-480D-9398-F1BCD8252322}">
   <ds:schemaRefs>
@@ -58653,17 +58653,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3425C370-B5F7-4368-9643-2B9A649E16D9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="477cc4b0-0066-4088-82a8-f8e908d5e20c"/>
-    <ds:schemaRef ds:uri="a2028d18-6aea-4b98-9583-fc23b0b95105"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B359544F-C9FF-40EB-8191-0AFB4CC45E2D}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -58682,6 +58671,17 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3425C370-B5F7-4368-9643-2B9A649E16D9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="477cc4b0-0066-4088-82a8-f8e908d5e20c"/>
+    <ds:schemaRef ds:uri="a2028d18-6aea-4b98-9583-fc23b0b95105"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{202412c0-1e7d-4ccc-99a7-7c8f0a21f86d}" enabled="1" method="Standard" siteId="{0d993ad3-fa73-421a-b129-1fe5590103f3}" contentBits="1" removed="0"/>
